--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F1E445F-66B8-4445-B294-3308DC7141CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{305482EC-CC77-4C7B-96E4-9A2ED2A6C449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2318" uniqueCount="322">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1060,24 +1060,6 @@
   </si>
   <si>
     <t>EN_STG4hbNREL_KE12-400</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_KE2-220</t>
-  </si>
-  <si>
-    <t>e_KE2-220</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_KE2-220</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w86402221-220</t>
-  </si>
-  <si>
-    <t>e_w86402221-220</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w86402221-220</t>
   </si>
   <si>
     <t>ELC</t>
@@ -2319,8 +2301,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4BEB33-B2E6-4680-AF95-AB1A7A7EB9E8}">
-  <dimension ref="B2:AJ83"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C14227FC-0B75-4F8C-A468-AB2FB24BA7C8}">
+  <dimension ref="B2:AJ79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:36" x14ac:dyDescent="0.45">
@@ -2455,25 +2437,25 @@
         <v>160</v>
       </c>
       <c r="AB4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="AC4" t="s">
+        <v>313</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>314</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>315</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH4" t="s">
         <v>319</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AI4" t="s">
         <v>320</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>321</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>322</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>325</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>326</v>
       </c>
       <c r="AJ4" t="s">
         <v>221</v>
@@ -2529,10 +2511,10 @@
         <v>221</v>
       </c>
       <c r="AA5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="AB5" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -2541,13 +2523,13 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AH5" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AI5" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AJ5" t="s">
         <v>208</v>
@@ -2603,10 +2585,10 @@
         <v>221</v>
       </c>
       <c r="AA6" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="AB6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="AD6">
         <v>2</v>
@@ -2615,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.45">
@@ -4921,62 +4903,6 @@
         <v>252</v>
       </c>
       <c r="X79" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="80" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U80" t="s">
-        <v>119</v>
-      </c>
-      <c r="V80" t="s">
-        <v>310</v>
-      </c>
-      <c r="W80" t="s">
-        <v>311</v>
-      </c>
-      <c r="X80" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="81" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U81" t="s">
-        <v>119</v>
-      </c>
-      <c r="V81" t="s">
-        <v>312</v>
-      </c>
-      <c r="W81" t="s">
-        <v>311</v>
-      </c>
-      <c r="X81" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="82" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U82" t="s">
-        <v>119</v>
-      </c>
-      <c r="V82" t="s">
-        <v>313</v>
-      </c>
-      <c r="W82" t="s">
-        <v>314</v>
-      </c>
-      <c r="X82" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="83" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U83" t="s">
-        <v>119</v>
-      </c>
-      <c r="V83" t="s">
-        <v>315</v>
-      </c>
-      <c r="W83" t="s">
-        <v>314</v>
-      </c>
-      <c r="X83" t="s">
         <v>221</v>
       </c>
     </row>
@@ -4986,7 +4912,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A2B8AC9-8645-4A9A-B7D6-8B8CB119F017}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{242AB7B5-556C-4FF8-BC69-38A214CB6C2B}">
   <dimension ref="B9:L26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55374814-4A1A-42A6-89FD-108C7D17DA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6339C11-BEFC-4C1A-9C94-6C8B48196D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2301,7 +2301,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFDE5256-46FE-4733-B554-FFC3CBF2EE9C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09F5CAC4-0B8E-4B70-AC2D-DDF15D6895F6}">
   <dimension ref="B2:AJ79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2404,7 +2404,7 @@
         <v>164</v>
       </c>
       <c r="J4">
-        <v>4.5331289763785171E-2</v>
+        <v>4.2872129394861049E-2</v>
       </c>
       <c r="K4" t="s">
         <v>165</v>
@@ -2481,7 +2481,7 @@
         <v>164</v>
       </c>
       <c r="J5">
-        <v>5.4283656844849162E-2</v>
+        <v>5.1338842825906901E-2</v>
       </c>
       <c r="K5" t="s">
         <v>165</v>
@@ -2555,7 +2555,7 @@
         <v>164</v>
       </c>
       <c r="J6">
-        <v>7.7600653704933922E-2</v>
+        <v>7.3390924549020339E-2</v>
       </c>
       <c r="K6" t="s">
         <v>165</v>
@@ -2620,7 +2620,7 @@
         <v>164</v>
       </c>
       <c r="J7">
-        <v>3.8145252255196264E-2</v>
+        <v>3.6075924576734038E-2</v>
       </c>
       <c r="K7" t="s">
         <v>165</v>
@@ -2670,7 +2670,7 @@
         <v>164</v>
       </c>
       <c r="J8">
-        <v>1.854002569801004E-2</v>
+        <v>3.506850940491605E-2</v>
       </c>
       <c r="K8" t="s">
         <v>165</v>
@@ -2720,7 +2720,7 @@
         <v>164</v>
       </c>
       <c r="J9">
-        <v>3.6832975849752869E-2</v>
+        <v>3.4834837368557296E-2</v>
       </c>
       <c r="K9" t="s">
         <v>165</v>
@@ -2770,7 +2770,7 @@
         <v>164</v>
       </c>
       <c r="J10">
-        <v>0.6081238618472028</v>
+        <v>0.57513397543001976</v>
       </c>
       <c r="K10" t="s">
         <v>165</v>
@@ -2820,7 +2820,7 @@
         <v>164</v>
       </c>
       <c r="J11">
-        <v>4.3210673215582016E-2</v>
+        <v>4.0866553389298642E-2</v>
       </c>
       <c r="K11" t="s">
         <v>165</v>
@@ -2870,7 +2870,7 @@
         <v>164</v>
       </c>
       <c r="J12">
-        <v>2.0258493025190154E-2</v>
+        <v>1.9159497531321068E-2</v>
       </c>
       <c r="K12" t="s">
         <v>165</v>
@@ -2920,7 +2920,7 @@
         <v>164</v>
       </c>
       <c r="J13">
-        <v>3.7673117795497479E-2</v>
+        <v>7.1258805529364339E-2</v>
       </c>
       <c r="K13" t="s">
         <v>165</v>
@@ -2970,7 +2970,7 @@
         <v>164</v>
       </c>
       <c r="J14">
-        <v>4.5331289763785171E-2</v>
+        <v>4.2872129394861049E-2</v>
       </c>
       <c r="K14" t="s">
         <v>165</v>
@@ -3020,7 +3020,7 @@
         <v>164</v>
       </c>
       <c r="J15">
-        <v>5.4283656844849162E-2</v>
+        <v>5.1338842825906901E-2</v>
       </c>
       <c r="K15" t="s">
         <v>165</v>
@@ -3070,7 +3070,7 @@
         <v>164</v>
       </c>
       <c r="J16">
-        <v>7.7600653704933922E-2</v>
+        <v>7.3390924549020339E-2</v>
       </c>
       <c r="K16" t="s">
         <v>165</v>
@@ -3120,7 +3120,7 @@
         <v>164</v>
       </c>
       <c r="J17">
-        <v>3.8145252255196264E-2</v>
+        <v>3.6075924576734038E-2</v>
       </c>
       <c r="K17" t="s">
         <v>165</v>
@@ -3170,7 +3170,7 @@
         <v>164</v>
       </c>
       <c r="J18">
-        <v>1.854002569801004E-2</v>
+        <v>3.506850940491605E-2</v>
       </c>
       <c r="K18" t="s">
         <v>165</v>
@@ -3220,7 +3220,7 @@
         <v>164</v>
       </c>
       <c r="J19">
-        <v>3.6832975849752869E-2</v>
+        <v>3.4834837368557296E-2</v>
       </c>
       <c r="K19" t="s">
         <v>165</v>
@@ -3270,7 +3270,7 @@
         <v>164</v>
       </c>
       <c r="J20">
-        <v>0.6081238618472028</v>
+        <v>0.57513397543001976</v>
       </c>
       <c r="K20" t="s">
         <v>165</v>
@@ -3320,7 +3320,7 @@
         <v>164</v>
       </c>
       <c r="J21">
-        <v>4.3210673215582016E-2</v>
+        <v>4.0866553389298642E-2</v>
       </c>
       <c r="K21" t="s">
         <v>165</v>
@@ -3370,7 +3370,7 @@
         <v>164</v>
       </c>
       <c r="J22">
-        <v>2.0258493025190154E-2</v>
+        <v>1.9159497531321068E-2</v>
       </c>
       <c r="K22" t="s">
         <v>165</v>
@@ -3420,7 +3420,7 @@
         <v>164</v>
       </c>
       <c r="J23">
-        <v>3.7673117795497479E-2</v>
+        <v>7.1258805529364339E-2</v>
       </c>
       <c r="K23" t="s">
         <v>165</v>
@@ -3470,7 +3470,7 @@
         <v>164</v>
       </c>
       <c r="J24">
-        <v>4.5331289763785171E-2</v>
+        <v>4.2872129394861049E-2</v>
       </c>
       <c r="K24" t="s">
         <v>165</v>
@@ -3520,7 +3520,7 @@
         <v>164</v>
       </c>
       <c r="J25">
-        <v>5.4283656844849162E-2</v>
+        <v>5.1338842825906901E-2</v>
       </c>
       <c r="K25" t="s">
         <v>165</v>
@@ -3570,7 +3570,7 @@
         <v>164</v>
       </c>
       <c r="J26">
-        <v>7.7600653704933922E-2</v>
+        <v>7.3390924549020339E-2</v>
       </c>
       <c r="K26" t="s">
         <v>165</v>
@@ -3620,7 +3620,7 @@
         <v>164</v>
       </c>
       <c r="J27">
-        <v>3.8145252255196264E-2</v>
+        <v>3.6075924576734038E-2</v>
       </c>
       <c r="K27" t="s">
         <v>165</v>
@@ -3670,7 +3670,7 @@
         <v>164</v>
       </c>
       <c r="J28">
-        <v>1.854002569801004E-2</v>
+        <v>3.506850940491605E-2</v>
       </c>
       <c r="K28" t="s">
         <v>165</v>
@@ -3720,7 +3720,7 @@
         <v>164</v>
       </c>
       <c r="J29">
-        <v>3.6832975849752869E-2</v>
+        <v>3.4834837368557296E-2</v>
       </c>
       <c r="K29" t="s">
         <v>165</v>
@@ -3770,7 +3770,7 @@
         <v>164</v>
       </c>
       <c r="J30">
-        <v>0.6081238618472028</v>
+        <v>0.57513397543001976</v>
       </c>
       <c r="K30" t="s">
         <v>165</v>
@@ -3820,7 +3820,7 @@
         <v>164</v>
       </c>
       <c r="J31">
-        <v>4.3210673215582016E-2</v>
+        <v>4.0866553389298642E-2</v>
       </c>
       <c r="K31" t="s">
         <v>165</v>
@@ -3870,7 +3870,7 @@
         <v>164</v>
       </c>
       <c r="J32">
-        <v>2.0258493025190154E-2</v>
+        <v>1.9159497531321068E-2</v>
       </c>
       <c r="K32" t="s">
         <v>165</v>
@@ -3920,7 +3920,7 @@
         <v>164</v>
       </c>
       <c r="J33">
-        <v>3.7673117795497479E-2</v>
+        <v>7.1258805529364339E-2</v>
       </c>
       <c r="K33" t="s">
         <v>165</v>
@@ -3970,7 +3970,7 @@
         <v>164</v>
       </c>
       <c r="J34">
-        <v>4.5331289763785171E-2</v>
+        <v>4.2872129394861049E-2</v>
       </c>
       <c r="K34" t="s">
         <v>165</v>
@@ -4020,7 +4020,7 @@
         <v>164</v>
       </c>
       <c r="J35">
-        <v>5.4283656844849162E-2</v>
+        <v>5.1338842825906901E-2</v>
       </c>
       <c r="K35" t="s">
         <v>165</v>
@@ -4070,7 +4070,7 @@
         <v>164</v>
       </c>
       <c r="J36">
-        <v>7.7600653704933922E-2</v>
+        <v>7.3390924549020339E-2</v>
       </c>
       <c r="K36" t="s">
         <v>165</v>
@@ -4120,7 +4120,7 @@
         <v>164</v>
       </c>
       <c r="J37">
-        <v>3.8145252255196264E-2</v>
+        <v>3.6075924576734038E-2</v>
       </c>
       <c r="K37" t="s">
         <v>165</v>
@@ -4170,7 +4170,7 @@
         <v>164</v>
       </c>
       <c r="J38">
-        <v>1.854002569801004E-2</v>
+        <v>3.506850940491605E-2</v>
       </c>
       <c r="K38" t="s">
         <v>165</v>
@@ -4220,7 +4220,7 @@
         <v>164</v>
       </c>
       <c r="J39">
-        <v>3.6832975849752869E-2</v>
+        <v>3.4834837368557296E-2</v>
       </c>
       <c r="K39" t="s">
         <v>165</v>
@@ -4258,7 +4258,7 @@
         <v>164</v>
       </c>
       <c r="J40">
-        <v>0.6081238618472028</v>
+        <v>0.57513397543001976</v>
       </c>
       <c r="K40" t="s">
         <v>165</v>
@@ -4296,7 +4296,7 @@
         <v>164</v>
       </c>
       <c r="J41">
-        <v>4.3210673215582016E-2</v>
+        <v>4.0866553389298642E-2</v>
       </c>
       <c r="K41" t="s">
         <v>165</v>
@@ -4334,7 +4334,7 @@
         <v>164</v>
       </c>
       <c r="J42">
-        <v>2.0258493025190154E-2</v>
+        <v>1.9159497531321068E-2</v>
       </c>
       <c r="K42" t="s">
         <v>165</v>
@@ -4372,7 +4372,7 @@
         <v>164</v>
       </c>
       <c r="J43">
-        <v>3.7673117795497479E-2</v>
+        <v>7.1258805529364339E-2</v>
       </c>
       <c r="K43" t="s">
         <v>165</v>
@@ -4912,7 +4912,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD726C53-03C5-4A27-B3EC-AC8BD70AD543}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4564F64A-CA29-4A1E-A1A6-3DA3121EBC16}">
   <dimension ref="B9:L26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6339C11-BEFC-4C1A-9C94-6C8B48196D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5578A4B8-273B-473F-9EAA-50B6D57C20C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="321">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -633,6 +633,9 @@
     <t>e_demand_w669520367-220</t>
   </si>
   <si>
+    <t>e_demand_w953567827-220</t>
+  </si>
+  <si>
     <t>e_demand_w1115312336-220</t>
   </si>
   <si>
@@ -651,9 +654,6 @@
     <t>e_demand_KE11-220</t>
   </si>
   <si>
-    <t>e_demand_KE3-220</t>
-  </si>
-  <si>
     <t>e_demand_w457973270-400</t>
   </si>
   <si>
@@ -663,6 +663,9 @@
     <t>ev_battery_w669520367-220</t>
   </si>
   <si>
+    <t>ev_battery_w953567827-220</t>
+  </si>
+  <si>
     <t>ev_battery_w1115312336-220</t>
   </si>
   <si>
@@ -681,9 +684,6 @@
     <t>ev_battery_KE11-220</t>
   </si>
   <si>
-    <t>ev_battery_KE3-220</t>
-  </si>
-  <si>
     <t>ev_battery_w457973270-400</t>
   </si>
   <si>
@@ -693,6 +693,9 @@
     <t>H2prd_Elc_PEM_w669520367-220</t>
   </si>
   <si>
+    <t>H2prd_Elc_PEM_w953567827-220</t>
+  </si>
+  <si>
     <t>H2prd_Elc_PEM_w1115312336-220</t>
   </si>
   <si>
@@ -711,9 +714,6 @@
     <t>H2prd_Elc_PEM_KE11-220</t>
   </si>
   <si>
-    <t>H2prd_Elc_PEM_KE3-220</t>
-  </si>
-  <si>
     <t>H2prd_Elc_PEM_w457973270-400</t>
   </si>
   <si>
@@ -723,6 +723,9 @@
     <t>H2prd_Elc_ALK_w669520367-220</t>
   </si>
   <si>
+    <t>H2prd_Elc_ALK_w953567827-220</t>
+  </si>
+  <si>
     <t>H2prd_Elc_ALK_w1115312336-220</t>
   </si>
   <si>
@@ -741,9 +744,6 @@
     <t>H2prd_Elc_ALK_KE11-220</t>
   </si>
   <si>
-    <t>H2prd_Elc_ALK_KE3-220</t>
-  </si>
-  <si>
     <t>H2prd_Elc_ALK_w457973270-400</t>
   </si>
   <si>
@@ -762,6 +762,9 @@
     <t>e_w669520367-220</t>
   </si>
   <si>
+    <t>e_w953567827-220</t>
+  </si>
+  <si>
     <t>e_w1115312336-220</t>
   </si>
   <si>
@@ -780,9 +783,6 @@
     <t>e_KE11-220</t>
   </si>
   <si>
-    <t>e_KE3-220</t>
-  </si>
-  <si>
     <t>e_w457973270-400</t>
   </si>
   <si>
@@ -943,9 +943,6 @@
   </si>
   <si>
     <t>EN_STG8hbNREL_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_w953567827-220</t>
   </si>
   <si>
     <t>EN_STG4hbNREL_w953567827-220</t>
@@ -2301,7 +2298,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09F5CAC4-0B8E-4B70-AC2D-DDF15D6895F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{113EBEC2-E2FF-44B2-9965-3ED0503D6390}">
   <dimension ref="B2:AJ79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2404,7 +2401,7 @@
         <v>164</v>
       </c>
       <c r="J4">
-        <v>4.2872129394861049E-2</v>
+        <v>4.3185124826726443E-2</v>
       </c>
       <c r="K4" t="s">
         <v>165</v>
@@ -2437,25 +2434,25 @@
         <v>160</v>
       </c>
       <c r="AB4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AC4" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD4" t="s">
         <v>313</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>314</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>315</v>
       </c>
-      <c r="AF4" t="s">
-        <v>316</v>
-      </c>
       <c r="AH4" t="s">
+        <v>318</v>
+      </c>
+      <c r="AI4" t="s">
         <v>319</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>320</v>
       </c>
       <c r="AJ4" t="s">
         <v>221</v>
@@ -2481,7 +2478,7 @@
         <v>164</v>
       </c>
       <c r="J5">
-        <v>5.1338842825906901E-2</v>
+        <v>5.1713650970698723E-2</v>
       </c>
       <c r="K5" t="s">
         <v>165</v>
@@ -2511,10 +2508,10 @@
         <v>221</v>
       </c>
       <c r="AA5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -2523,13 +2520,13 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AH5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AI5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AJ5" t="s">
         <v>208</v>
@@ -2555,7 +2552,7 @@
         <v>164</v>
       </c>
       <c r="J6">
-        <v>7.3390924549020339E-2</v>
+        <v>1.2144714448026258E-2</v>
       </c>
       <c r="K6" t="s">
         <v>165</v>
@@ -2585,10 +2582,10 @@
         <v>221</v>
       </c>
       <c r="AA6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AD6">
         <v>2</v>
@@ -2597,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.45">
@@ -2620,7 +2617,7 @@
         <v>164</v>
       </c>
       <c r="J7">
-        <v>3.6075924576734038E-2</v>
+        <v>7.392672774910522E-2</v>
       </c>
       <c r="K7" t="s">
         <v>165</v>
@@ -2670,7 +2667,7 @@
         <v>164</v>
       </c>
       <c r="J8">
-        <v>3.506850940491605E-2</v>
+        <v>3.633930313413767E-2</v>
       </c>
       <c r="K8" t="s">
         <v>165</v>
@@ -2720,7 +2717,7 @@
         <v>164</v>
       </c>
       <c r="J9">
-        <v>3.4834837368557296E-2</v>
+        <v>3.5324533152767991E-2</v>
       </c>
       <c r="K9" t="s">
         <v>165</v>
@@ -2770,7 +2767,7 @@
         <v>164</v>
       </c>
       <c r="J10">
-        <v>0.57513397543001976</v>
+        <v>3.5089155153095367E-2</v>
       </c>
       <c r="K10" t="s">
         <v>165</v>
@@ -2820,7 +2817,7 @@
         <v>164</v>
       </c>
       <c r="J11">
-        <v>4.0866553389298642E-2</v>
+        <v>0.57933284097649596</v>
       </c>
       <c r="K11" t="s">
         <v>165</v>
@@ -2870,7 +2867,7 @@
         <v>164</v>
       </c>
       <c r="J12">
-        <v>1.9159497531321068E-2</v>
+        <v>4.1164906764964301E-2</v>
       </c>
       <c r="K12" t="s">
         <v>165</v>
@@ -2920,7 +2917,7 @@
         <v>164</v>
       </c>
       <c r="J13">
-        <v>7.1258805529364339E-2</v>
+        <v>7.1779042823981773E-2</v>
       </c>
       <c r="K13" t="s">
         <v>165</v>
@@ -2970,7 +2967,7 @@
         <v>164</v>
       </c>
       <c r="J14">
-        <v>4.2872129394861049E-2</v>
+        <v>4.3185124826726443E-2</v>
       </c>
       <c r="K14" t="s">
         <v>165</v>
@@ -3020,7 +3017,7 @@
         <v>164</v>
       </c>
       <c r="J15">
-        <v>5.1338842825906901E-2</v>
+        <v>5.1713650970698723E-2</v>
       </c>
       <c r="K15" t="s">
         <v>165</v>
@@ -3070,7 +3067,7 @@
         <v>164</v>
       </c>
       <c r="J16">
-        <v>7.3390924549020339E-2</v>
+        <v>1.2144714448026258E-2</v>
       </c>
       <c r="K16" t="s">
         <v>165</v>
@@ -3120,7 +3117,7 @@
         <v>164</v>
       </c>
       <c r="J17">
-        <v>3.6075924576734038E-2</v>
+        <v>7.392672774910522E-2</v>
       </c>
       <c r="K17" t="s">
         <v>165</v>
@@ -3144,7 +3141,7 @@
         <v>234</v>
       </c>
       <c r="W17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="X17" t="s">
         <v>221</v>
@@ -3170,7 +3167,7 @@
         <v>164</v>
       </c>
       <c r="J18">
-        <v>3.506850940491605E-2</v>
+        <v>3.633930313413767E-2</v>
       </c>
       <c r="K18" t="s">
         <v>165</v>
@@ -3194,7 +3191,7 @@
         <v>235</v>
       </c>
       <c r="W18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="X18" t="s">
         <v>221</v>
@@ -3220,7 +3217,7 @@
         <v>164</v>
       </c>
       <c r="J19">
-        <v>3.4834837368557296E-2</v>
+        <v>3.5324533152767991E-2</v>
       </c>
       <c r="K19" t="s">
         <v>165</v>
@@ -3244,7 +3241,7 @@
         <v>236</v>
       </c>
       <c r="W19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="X19" t="s">
         <v>221</v>
@@ -3270,7 +3267,7 @@
         <v>164</v>
       </c>
       <c r="J20">
-        <v>0.57513397543001976</v>
+        <v>3.5089155153095367E-2</v>
       </c>
       <c r="K20" t="s">
         <v>165</v>
@@ -3320,7 +3317,7 @@
         <v>164</v>
       </c>
       <c r="J21">
-        <v>4.0866553389298642E-2</v>
+        <v>0.57933284097649596</v>
       </c>
       <c r="K21" t="s">
         <v>165</v>
@@ -3370,7 +3367,7 @@
         <v>164</v>
       </c>
       <c r="J22">
-        <v>1.9159497531321068E-2</v>
+        <v>4.1164906764964301E-2</v>
       </c>
       <c r="K22" t="s">
         <v>165</v>
@@ -3420,7 +3417,7 @@
         <v>164</v>
       </c>
       <c r="J23">
-        <v>7.1258805529364339E-2</v>
+        <v>7.1779042823981773E-2</v>
       </c>
       <c r="K23" t="s">
         <v>165</v>
@@ -3470,7 +3467,7 @@
         <v>164</v>
       </c>
       <c r="J24">
-        <v>4.2872129394861049E-2</v>
+        <v>4.3185124826726443E-2</v>
       </c>
       <c r="K24" t="s">
         <v>165</v>
@@ -3520,7 +3517,7 @@
         <v>164</v>
       </c>
       <c r="J25">
-        <v>5.1338842825906901E-2</v>
+        <v>5.1713650970698723E-2</v>
       </c>
       <c r="K25" t="s">
         <v>165</v>
@@ -3570,7 +3567,7 @@
         <v>164</v>
       </c>
       <c r="J26">
-        <v>7.3390924549020339E-2</v>
+        <v>1.2144714448026258E-2</v>
       </c>
       <c r="K26" t="s">
         <v>165</v>
@@ -3620,7 +3617,7 @@
         <v>164</v>
       </c>
       <c r="J27">
-        <v>3.6075924576734038E-2</v>
+        <v>7.392672774910522E-2</v>
       </c>
       <c r="K27" t="s">
         <v>165</v>
@@ -3670,7 +3667,7 @@
         <v>164</v>
       </c>
       <c r="J28">
-        <v>3.506850940491605E-2</v>
+        <v>3.633930313413767E-2</v>
       </c>
       <c r="K28" t="s">
         <v>165</v>
@@ -3720,7 +3717,7 @@
         <v>164</v>
       </c>
       <c r="J29">
-        <v>3.4834837368557296E-2</v>
+        <v>3.5324533152767991E-2</v>
       </c>
       <c r="K29" t="s">
         <v>165</v>
@@ -3744,7 +3741,7 @@
         <v>248</v>
       </c>
       <c r="W29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="X29" t="s">
         <v>221</v>
@@ -3770,7 +3767,7 @@
         <v>164</v>
       </c>
       <c r="J30">
-        <v>0.57513397543001976</v>
+        <v>3.5089155153095367E-2</v>
       </c>
       <c r="K30" t="s">
         <v>165</v>
@@ -3794,7 +3791,7 @@
         <v>249</v>
       </c>
       <c r="W30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="X30" t="s">
         <v>221</v>
@@ -3820,7 +3817,7 @@
         <v>164</v>
       </c>
       <c r="J31">
-        <v>4.0866553389298642E-2</v>
+        <v>0.57933284097649596</v>
       </c>
       <c r="K31" t="s">
         <v>165</v>
@@ -3844,7 +3841,7 @@
         <v>250</v>
       </c>
       <c r="W31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="X31" t="s">
         <v>221</v>
@@ -3870,7 +3867,7 @@
         <v>164</v>
       </c>
       <c r="J32">
-        <v>1.9159497531321068E-2</v>
+        <v>4.1164906764964301E-2</v>
       </c>
       <c r="K32" t="s">
         <v>165</v>
@@ -3920,7 +3917,7 @@
         <v>164</v>
       </c>
       <c r="J33">
-        <v>7.1258805529364339E-2</v>
+        <v>7.1779042823981773E-2</v>
       </c>
       <c r="K33" t="s">
         <v>165</v>
@@ -3970,7 +3967,7 @@
         <v>164</v>
       </c>
       <c r="J34">
-        <v>4.2872129394861049E-2</v>
+        <v>4.3185124826726443E-2</v>
       </c>
       <c r="K34" t="s">
         <v>165</v>
@@ -4020,7 +4017,7 @@
         <v>164</v>
       </c>
       <c r="J35">
-        <v>5.1338842825906901E-2</v>
+        <v>5.1713650970698723E-2</v>
       </c>
       <c r="K35" t="s">
         <v>165</v>
@@ -4070,7 +4067,7 @@
         <v>164</v>
       </c>
       <c r="J36">
-        <v>7.3390924549020339E-2</v>
+        <v>1.2144714448026258E-2</v>
       </c>
       <c r="K36" t="s">
         <v>165</v>
@@ -4120,7 +4117,7 @@
         <v>164</v>
       </c>
       <c r="J37">
-        <v>3.6075924576734038E-2</v>
+        <v>7.392672774910522E-2</v>
       </c>
       <c r="K37" t="s">
         <v>165</v>
@@ -4170,7 +4167,7 @@
         <v>164</v>
       </c>
       <c r="J38">
-        <v>3.506850940491605E-2</v>
+        <v>3.633930313413767E-2</v>
       </c>
       <c r="K38" t="s">
         <v>165</v>
@@ -4220,7 +4217,7 @@
         <v>164</v>
       </c>
       <c r="J39">
-        <v>3.4834837368557296E-2</v>
+        <v>3.5324533152767991E-2</v>
       </c>
       <c r="K39" t="s">
         <v>165</v>
@@ -4258,7 +4255,7 @@
         <v>164</v>
       </c>
       <c r="J40">
-        <v>0.57513397543001976</v>
+        <v>3.5089155153095367E-2</v>
       </c>
       <c r="K40" t="s">
         <v>165</v>
@@ -4282,7 +4279,7 @@
         <v>261</v>
       </c>
       <c r="W40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="X40" t="s">
         <v>221</v>
@@ -4296,7 +4293,7 @@
         <v>164</v>
       </c>
       <c r="J41">
-        <v>4.0866553389298642E-2</v>
+        <v>0.57933284097649596</v>
       </c>
       <c r="K41" t="s">
         <v>165</v>
@@ -4320,7 +4317,7 @@
         <v>262</v>
       </c>
       <c r="W41" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="X41" t="s">
         <v>221</v>
@@ -4334,7 +4331,7 @@
         <v>164</v>
       </c>
       <c r="J42">
-        <v>1.9159497531321068E-2</v>
+        <v>4.1164906764964301E-2</v>
       </c>
       <c r="K42" t="s">
         <v>165</v>
@@ -4358,7 +4355,7 @@
         <v>263</v>
       </c>
       <c r="W42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="X42" t="s">
         <v>221</v>
@@ -4372,7 +4369,7 @@
         <v>164</v>
       </c>
       <c r="J43">
-        <v>7.1258805529364339E-2</v>
+        <v>7.1779042823981773E-2</v>
       </c>
       <c r="K43" t="s">
         <v>165</v>
@@ -4396,7 +4393,7 @@
         <v>264</v>
       </c>
       <c r="W43" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="X43" t="s">
         <v>221</v>
@@ -4438,7 +4435,7 @@
         <v>268</v>
       </c>
       <c r="W46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="X46" t="s">
         <v>221</v>
@@ -4452,7 +4449,7 @@
         <v>269</v>
       </c>
       <c r="W47" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="X47" t="s">
         <v>221</v>
@@ -4466,7 +4463,7 @@
         <v>270</v>
       </c>
       <c r="W48" t="s">
-        <v>271</v>
+        <v>210</v>
       </c>
       <c r="X48" t="s">
         <v>221</v>
@@ -4477,10 +4474,10 @@
         <v>119</v>
       </c>
       <c r="V49" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="W49" t="s">
-        <v>271</v>
+        <v>210</v>
       </c>
       <c r="X49" t="s">
         <v>221</v>
@@ -4491,10 +4488,10 @@
         <v>119</v>
       </c>
       <c r="V50" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="W50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="X50" t="s">
         <v>221</v>
@@ -4505,10 +4502,10 @@
         <v>119</v>
       </c>
       <c r="V51" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="W51" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="X51" t="s">
         <v>221</v>
@@ -4519,10 +4516,10 @@
         <v>119</v>
       </c>
       <c r="V52" t="s">
+        <v>274</v>
+      </c>
+      <c r="W52" t="s">
         <v>275</v>
-      </c>
-      <c r="W52" t="s">
-        <v>276</v>
       </c>
       <c r="X52" t="s">
         <v>221</v>
@@ -4533,10 +4530,10 @@
         <v>119</v>
       </c>
       <c r="V53" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="W53" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="X53" t="s">
         <v>221</v>
@@ -4547,7 +4544,7 @@
         <v>119</v>
       </c>
       <c r="V54" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="W54" t="s">
         <v>217</v>
@@ -4561,7 +4558,7 @@
         <v>119</v>
       </c>
       <c r="V55" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="W55" t="s">
         <v>217</v>
@@ -4575,10 +4572,10 @@
         <v>119</v>
       </c>
       <c r="V56" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W56" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="X56" t="s">
         <v>221</v>
@@ -4589,10 +4586,10 @@
         <v>119</v>
       </c>
       <c r="V57" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="W57" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="X57" t="s">
         <v>221</v>
@@ -4603,7 +4600,7 @@
         <v>119</v>
       </c>
       <c r="V58" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="W58" t="s">
         <v>256</v>
@@ -4617,7 +4614,7 @@
         <v>119</v>
       </c>
       <c r="V59" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W59" t="s">
         <v>256</v>
@@ -4631,10 +4628,10 @@
         <v>119</v>
       </c>
       <c r="V60" t="s">
+        <v>283</v>
+      </c>
+      <c r="W60" t="s">
         <v>284</v>
-      </c>
-      <c r="W60" t="s">
-        <v>285</v>
       </c>
       <c r="X60" t="s">
         <v>221</v>
@@ -4645,10 +4642,10 @@
         <v>119</v>
       </c>
       <c r="V61" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="W61" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="X61" t="s">
         <v>221</v>
@@ -4659,10 +4656,10 @@
         <v>119</v>
       </c>
       <c r="V62" t="s">
+        <v>286</v>
+      </c>
+      <c r="W62" t="s">
         <v>287</v>
-      </c>
-      <c r="W62" t="s">
-        <v>288</v>
       </c>
       <c r="X62" t="s">
         <v>221</v>
@@ -4673,10 +4670,10 @@
         <v>119</v>
       </c>
       <c r="V63" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="W63" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="X63" t="s">
         <v>221</v>
@@ -4687,10 +4684,10 @@
         <v>119</v>
       </c>
       <c r="V64" t="s">
+        <v>289</v>
+      </c>
+      <c r="W64" t="s">
         <v>290</v>
-      </c>
-      <c r="W64" t="s">
-        <v>291</v>
       </c>
       <c r="X64" t="s">
         <v>221</v>
@@ -4701,10 +4698,10 @@
         <v>119</v>
       </c>
       <c r="V65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="W65" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="X65" t="s">
         <v>221</v>
@@ -4715,10 +4712,10 @@
         <v>119</v>
       </c>
       <c r="V66" t="s">
+        <v>292</v>
+      </c>
+      <c r="W66" t="s">
         <v>293</v>
-      </c>
-      <c r="W66" t="s">
-        <v>294</v>
       </c>
       <c r="X66" t="s">
         <v>221</v>
@@ -4729,10 +4726,10 @@
         <v>119</v>
       </c>
       <c r="V67" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="W67" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="X67" t="s">
         <v>221</v>
@@ -4743,10 +4740,10 @@
         <v>119</v>
       </c>
       <c r="V68" t="s">
+        <v>295</v>
+      </c>
+      <c r="W68" t="s">
         <v>296</v>
-      </c>
-      <c r="W68" t="s">
-        <v>297</v>
       </c>
       <c r="X68" t="s">
         <v>221</v>
@@ -4757,10 +4754,10 @@
         <v>119</v>
       </c>
       <c r="V69" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="W69" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="X69" t="s">
         <v>221</v>
@@ -4771,10 +4768,10 @@
         <v>119</v>
       </c>
       <c r="V70" t="s">
+        <v>298</v>
+      </c>
+      <c r="W70" t="s">
         <v>299</v>
-      </c>
-      <c r="W70" t="s">
-        <v>300</v>
       </c>
       <c r="X70" t="s">
         <v>221</v>
@@ -4785,10 +4782,10 @@
         <v>119</v>
       </c>
       <c r="V71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="W71" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="X71" t="s">
         <v>221</v>
@@ -4799,7 +4796,7 @@
         <v>119</v>
       </c>
       <c r="V72" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="W72" t="s">
         <v>238</v>
@@ -4813,7 +4810,7 @@
         <v>119</v>
       </c>
       <c r="V73" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="W73" t="s">
         <v>238</v>
@@ -4827,7 +4824,7 @@
         <v>119</v>
       </c>
       <c r="V74" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="W74" t="s">
         <v>209</v>
@@ -4841,7 +4838,7 @@
         <v>119</v>
       </c>
       <c r="V75" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="W75" t="s">
         <v>209</v>
@@ -4855,7 +4852,7 @@
         <v>119</v>
       </c>
       <c r="V76" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="W76" t="s">
         <v>245</v>
@@ -4869,7 +4866,7 @@
         <v>119</v>
       </c>
       <c r="V77" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="W77" t="s">
         <v>245</v>
@@ -4883,7 +4880,7 @@
         <v>119</v>
       </c>
       <c r="V78" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="W78" t="s">
         <v>252</v>
@@ -4897,7 +4894,7 @@
         <v>119</v>
       </c>
       <c r="V79" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="W79" t="s">
         <v>252</v>
@@ -4912,7 +4909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4564F64A-CA29-4A1E-A1A6-3DA3121EBC16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E01A8D8-1ADC-4CEA-885C-1376FADFE64F}">
   <dimension ref="B9:L26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5578A4B8-273B-473F-9EAA-50B6D57C20C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48EA56E-6248-4C0B-B4AC-56446B1BBC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="318">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1084,15 +1084,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -2299,10 +2290,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{113EBEC2-E2FF-44B2-9965-3ED0503D6390}">
-  <dimension ref="B2:AJ79"/>
+  <dimension ref="B2:AF79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -2315,11 +2306,8 @@
       <c r="U2" t="s">
         <v>205</v>
       </c>
-      <c r="AH2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -2371,17 +2359,8 @@
       <c r="AA3" t="s">
         <v>159</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>160</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>123</v>
       </c>
@@ -2448,17 +2427,8 @@
       <c r="AF4" t="s">
         <v>315</v>
       </c>
-      <c r="AH4" t="s">
-        <v>318</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>319</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>124</v>
       </c>
@@ -2522,17 +2492,8 @@
       <c r="AF5" t="s">
         <v>316</v>
       </c>
-      <c r="AH5" t="s">
-        <v>320</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>319</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>125</v>
       </c>
@@ -2597,7 +2558,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>126</v>
       </c>
@@ -2647,7 +2608,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>127</v>
       </c>
@@ -2697,7 +2658,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>128</v>
       </c>
@@ -2747,7 +2708,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>129</v>
       </c>
@@ -2797,7 +2758,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>130</v>
       </c>
@@ -2847,7 +2808,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>131</v>
       </c>
@@ -2897,7 +2858,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>132</v>
       </c>
@@ -2947,7 +2908,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>133</v>
       </c>
@@ -2997,7 +2958,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>134</v>
       </c>
@@ -3047,7 +3008,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>135</v>
       </c>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48EA56E-6248-4C0B-B4AC-56446B1BBC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA5FF30A-1E1D-4FC7-A2A1-FD949DE3438E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="321">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1084,6 +1084,15 @@
   </si>
   <si>
     <t>STG</t>
+  </si>
+  <si>
+    <t>Trd_electricity import</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -2289,11 +2298,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{113EBEC2-E2FF-44B2-9965-3ED0503D6390}">
-  <dimension ref="B2:AF79"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1709EBF5-C7D9-4330-8B25-5D9D336DD13E}">
+  <dimension ref="B2:AJ79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -2306,8 +2315,11 @@
       <c r="U2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -2359,8 +2371,17 @@
       <c r="AA3" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>160</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>123</v>
       </c>
@@ -2427,8 +2448,17 @@
       <c r="AF4" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH4" t="s">
+        <v>318</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>319</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>124</v>
       </c>
@@ -2492,8 +2522,17 @@
       <c r="AF5" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH5" t="s">
+        <v>320</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>319</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>125</v>
       </c>
@@ -2558,7 +2597,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>126</v>
       </c>
@@ -2608,7 +2647,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>127</v>
       </c>
@@ -2658,7 +2697,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>128</v>
       </c>
@@ -2708,7 +2747,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>129</v>
       </c>
@@ -2758,7 +2797,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>130</v>
       </c>
@@ -2808,7 +2847,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>131</v>
       </c>
@@ -2858,7 +2897,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>132</v>
       </c>
@@ -2908,7 +2947,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>133</v>
       </c>
@@ -2958,7 +2997,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>134</v>
       </c>
@@ -3008,7 +3047,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>135</v>
       </c>
@@ -4870,7 +4909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E01A8D8-1ADC-4CEA-885C-1376FADFE64F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FAEFE6D-F360-4980-9FCF-740E80F958B9}">
   <dimension ref="B9:L26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA5FF30A-1E1D-4FC7-A2A1-FD949DE3438E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B203D941-D943-42FF-B34A-964F68DF6693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="318">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1084,15 +1084,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -2298,11 +2289,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1709EBF5-C7D9-4330-8B25-5D9D336DD13E}">
-  <dimension ref="B2:AJ79"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5359260F-4DC9-48C1-9C60-AC50A47DE7B2}">
+  <dimension ref="B2:AF79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -2315,11 +2306,8 @@
       <c r="U2" t="s">
         <v>205</v>
       </c>
-      <c r="AH2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -2371,17 +2359,8 @@
       <c r="AA3" t="s">
         <v>159</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>160</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>123</v>
       </c>
@@ -2448,17 +2427,8 @@
       <c r="AF4" t="s">
         <v>315</v>
       </c>
-      <c r="AH4" t="s">
-        <v>318</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>319</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>124</v>
       </c>
@@ -2522,17 +2492,8 @@
       <c r="AF5" t="s">
         <v>316</v>
       </c>
-      <c r="AH5" t="s">
-        <v>320</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>319</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>125</v>
       </c>
@@ -2597,7 +2558,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>126</v>
       </c>
@@ -2647,7 +2608,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>127</v>
       </c>
@@ -2697,7 +2658,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>128</v>
       </c>
@@ -2747,7 +2708,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>129</v>
       </c>
@@ -2797,7 +2758,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>130</v>
       </c>
@@ -2847,7 +2808,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>131</v>
       </c>
@@ -2897,7 +2858,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>132</v>
       </c>
@@ -2947,7 +2908,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>133</v>
       </c>
@@ -2997,7 +2958,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>134</v>
       </c>
@@ -3047,7 +3008,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>135</v>
       </c>
@@ -4909,7 +4870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FAEFE6D-F360-4980-9FCF-740E80F958B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6C4547-D6D5-42E4-8030-6A22AF65CAFC}">
   <dimension ref="B9:L26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B203D941-D943-42FF-B34A-964F68DF6693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8A5F1E8-5FEE-448C-A94F-000E23866C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2289,7 +2289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5359260F-4DC9-48C1-9C60-AC50A47DE7B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877A6333-0464-4EC5-991B-E1B8D5F11AB4}">
   <dimension ref="B2:AF79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4870,7 +4870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6C4547-D6D5-42E4-8030-6A22AF65CAFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB447BB-E8CA-4214-9E20-B3262CBB4470}">
   <dimension ref="B9:L26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8A5F1E8-5FEE-448C-A94F-000E23866C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CE03EC-3BD3-45F1-8F33-C6D7C4DF7D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="319">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1084,6 +1084,9 @@
   </si>
   <si>
     <t>STG</t>
+  </si>
+  <si>
+    <t>UCE_min oil fleet utilization</t>
   </si>
 </sst>
 </file>
@@ -1954,6 +1957,30 @@
       <c r="J10" s="3">
         <v>0.22132714596479999</v>
       </c>
+      <c r="AF10" t="s">
+        <v>318</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH10">
+        <f>-1/8.76</f>
+        <v>-0.11415525114155252</v>
+      </c>
+      <c r="AI10" s="2">
+        <f>VLOOKUP(AG10,$F$3:$J$11,2,FALSE)</f>
+        <v>0.10772396938709886</v>
+      </c>
+      <c r="AJ10">
+        <f>AI10*$AD$1</f>
+        <v>2.1544793877419772E-2</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CE03EC-3BD3-45F1-8F33-C6D7C4DF7D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BA0189F-24EA-4219-853B-C5CA98F04937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Veda" sheetId="1" r:id="rId1"/>
-    <sheet name="grids" sheetId="6" r:id="rId2"/>
-    <sheet name="re_targets" sheetId="5" r:id="rId3"/>
+    <sheet name="grids" sheetId="6" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="5" r:id="rId2"/>
+    <sheet name="Veda" sheetId="1" r:id="rId3"/>
     <sheet name="buildrates" sheetId="4" r:id="rId4"/>
     <sheet name="historical_data_long" sheetId="3" r:id="rId5"/>
   </sheets>
@@ -391,6 +391,9 @@
     <t>\I: hydro</t>
   </si>
   <si>
+    <t>UCE_min oil fleet utilization</t>
+  </si>
+  <si>
     <t>geothermal</t>
   </si>
   <si>
@@ -1084,17 +1087,15 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>UCE_min oil fleet utilization</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1222,7 +1223,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1235,6 +1236,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1576,6 +1578,3197 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734D939D-8184-435E-B479-8BDCF3F17917}">
+  <dimension ref="B2:AF79"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>160</v>
+      </c>
+      <c r="P2" t="s">
+        <v>206</v>
+      </c>
+      <c r="U2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K3" t="s">
+        <v>163</v>
+      </c>
+      <c r="L3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>161</v>
+      </c>
+      <c r="R3" t="s">
+        <v>207</v>
+      </c>
+      <c r="U3" t="s">
+        <v>219</v>
+      </c>
+      <c r="V3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W3" t="s">
+        <v>161</v>
+      </c>
+      <c r="X3" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4">
+        <v>3.5749528668221644</v>
+      </c>
+      <c r="D4">
+        <v>433.40000000000003</v>
+      </c>
+      <c r="E4">
+        <v>0.97636000000000001</v>
+      </c>
+      <c r="H4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J4">
+        <v>4.3185124826726443E-2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>166</v>
+      </c>
+      <c r="L4" t="s">
+        <v>165</v>
+      </c>
+      <c r="P4" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>208</v>
+      </c>
+      <c r="R4" t="s">
+        <v>209</v>
+      </c>
+      <c r="U4" t="s">
+        <v>120</v>
+      </c>
+      <c r="V4" t="s">
+        <v>220</v>
+      </c>
+      <c r="W4" t="s">
+        <v>221</v>
+      </c>
+      <c r="X4" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>311</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>313</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>314</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>315</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5">
+        <v>3.5749528668221644</v>
+      </c>
+      <c r="D5">
+        <v>218.9</v>
+      </c>
+      <c r="E5">
+        <v>0.98806000000000005</v>
+      </c>
+      <c r="H5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I5" t="s">
+        <v>165</v>
+      </c>
+      <c r="J5">
+        <v>5.1713650970698723E-2</v>
+      </c>
+      <c r="K5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L5" t="s">
+        <v>165</v>
+      </c>
+      <c r="P5" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>210</v>
+      </c>
+      <c r="R5" t="s">
+        <v>209</v>
+      </c>
+      <c r="U5" t="s">
+        <v>120</v>
+      </c>
+      <c r="V5" t="s">
+        <v>223</v>
+      </c>
+      <c r="W5" t="s">
+        <v>221</v>
+      </c>
+      <c r="X5" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>312</v>
+      </c>
+      <c r="AC5">
+        <v>2</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D6">
+        <v>136.4</v>
+      </c>
+      <c r="E6">
+        <v>0.99256</v>
+      </c>
+      <c r="H6" t="s">
+        <v>168</v>
+      </c>
+      <c r="I6" t="s">
+        <v>165</v>
+      </c>
+      <c r="J6">
+        <v>1.2144714448026258E-2</v>
+      </c>
+      <c r="K6" t="s">
+        <v>166</v>
+      </c>
+      <c r="L6" t="s">
+        <v>165</v>
+      </c>
+      <c r="P6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>211</v>
+      </c>
+      <c r="R6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U6" t="s">
+        <v>120</v>
+      </c>
+      <c r="V6" t="s">
+        <v>224</v>
+      </c>
+      <c r="W6" t="s">
+        <v>221</v>
+      </c>
+      <c r="X6" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD6">
+        <v>2</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D7">
+        <v>30.800000000000004</v>
+      </c>
+      <c r="E7">
+        <v>0.99831999999999999</v>
+      </c>
+      <c r="H7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I7" t="s">
+        <v>165</v>
+      </c>
+      <c r="J7">
+        <v>7.392672774910522E-2</v>
+      </c>
+      <c r="K7" t="s">
+        <v>166</v>
+      </c>
+      <c r="L7" t="s">
+        <v>165</v>
+      </c>
+      <c r="P7" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>212</v>
+      </c>
+      <c r="R7" t="s">
+        <v>209</v>
+      </c>
+      <c r="U7" t="s">
+        <v>120</v>
+      </c>
+      <c r="V7" t="s">
+        <v>225</v>
+      </c>
+      <c r="W7" t="s">
+        <v>221</v>
+      </c>
+      <c r="X7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E8">
+        <v>0.99994000000000005</v>
+      </c>
+      <c r="H8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" t="s">
+        <v>165</v>
+      </c>
+      <c r="J8">
+        <v>3.633930313413767E-2</v>
+      </c>
+      <c r="K8" t="s">
+        <v>166</v>
+      </c>
+      <c r="L8" t="s">
+        <v>165</v>
+      </c>
+      <c r="P8" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>213</v>
+      </c>
+      <c r="R8" t="s">
+        <v>209</v>
+      </c>
+      <c r="U8" t="s">
+        <v>120</v>
+      </c>
+      <c r="V8" t="s">
+        <v>226</v>
+      </c>
+      <c r="W8" t="s">
+        <v>221</v>
+      </c>
+      <c r="X8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D9">
+        <v>7.7000000000000011</v>
+      </c>
+      <c r="E9">
+        <v>0.99958000000000002</v>
+      </c>
+      <c r="H9" t="s">
+        <v>171</v>
+      </c>
+      <c r="I9" t="s">
+        <v>165</v>
+      </c>
+      <c r="J9">
+        <v>3.5324533152767991E-2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>166</v>
+      </c>
+      <c r="L9" t="s">
+        <v>165</v>
+      </c>
+      <c r="P9" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>214</v>
+      </c>
+      <c r="R9" t="s">
+        <v>209</v>
+      </c>
+      <c r="U9" t="s">
+        <v>120</v>
+      </c>
+      <c r="V9" t="s">
+        <v>227</v>
+      </c>
+      <c r="W9" t="s">
+        <v>221</v>
+      </c>
+      <c r="X9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D10">
+        <v>26.400000000000002</v>
+      </c>
+      <c r="E10">
+        <v>0.99856</v>
+      </c>
+      <c r="H10" t="s">
+        <v>172</v>
+      </c>
+      <c r="I10" t="s">
+        <v>165</v>
+      </c>
+      <c r="J10">
+        <v>3.5089155153095367E-2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>166</v>
+      </c>
+      <c r="L10" t="s">
+        <v>165</v>
+      </c>
+      <c r="P10" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>215</v>
+      </c>
+      <c r="R10" t="s">
+        <v>209</v>
+      </c>
+      <c r="U10" t="s">
+        <v>120</v>
+      </c>
+      <c r="V10" t="s">
+        <v>228</v>
+      </c>
+      <c r="W10" t="s">
+        <v>221</v>
+      </c>
+      <c r="X10" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D11">
+        <v>22</v>
+      </c>
+      <c r="E11">
+        <v>0.99880000000000002</v>
+      </c>
+      <c r="H11" t="s">
+        <v>173</v>
+      </c>
+      <c r="I11" t="s">
+        <v>165</v>
+      </c>
+      <c r="J11">
+        <v>0.57933284097649596</v>
+      </c>
+      <c r="K11" t="s">
+        <v>166</v>
+      </c>
+      <c r="L11" t="s">
+        <v>165</v>
+      </c>
+      <c r="P11" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>216</v>
+      </c>
+      <c r="R11" t="s">
+        <v>209</v>
+      </c>
+      <c r="U11" t="s">
+        <v>120</v>
+      </c>
+      <c r="V11" t="s">
+        <v>229</v>
+      </c>
+      <c r="W11" t="s">
+        <v>221</v>
+      </c>
+      <c r="X11" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D12">
+        <v>221.10000000000002</v>
+      </c>
+      <c r="E12">
+        <v>0.98794000000000004</v>
+      </c>
+      <c r="H12" t="s">
+        <v>174</v>
+      </c>
+      <c r="I12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J12">
+        <v>4.1164906764964301E-2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>166</v>
+      </c>
+      <c r="L12" t="s">
+        <v>165</v>
+      </c>
+      <c r="P12" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>217</v>
+      </c>
+      <c r="R12" t="s">
+        <v>209</v>
+      </c>
+      <c r="U12" t="s">
+        <v>120</v>
+      </c>
+      <c r="V12" t="s">
+        <v>230</v>
+      </c>
+      <c r="W12" t="s">
+        <v>221</v>
+      </c>
+      <c r="X12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13">
+        <v>3.5749528668221644</v>
+      </c>
+      <c r="D13">
+        <v>248.60000000000002</v>
+      </c>
+      <c r="E13">
+        <v>0.98643999999999998</v>
+      </c>
+      <c r="H13" t="s">
+        <v>175</v>
+      </c>
+      <c r="I13" t="s">
+        <v>165</v>
+      </c>
+      <c r="J13">
+        <v>7.1779042823981773E-2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s">
+        <v>165</v>
+      </c>
+      <c r="P13" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>218</v>
+      </c>
+      <c r="R13" t="s">
+        <v>209</v>
+      </c>
+      <c r="U13" t="s">
+        <v>120</v>
+      </c>
+      <c r="V13" t="s">
+        <v>231</v>
+      </c>
+      <c r="W13" t="s">
+        <v>221</v>
+      </c>
+      <c r="X13" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D14">
+        <v>82.5</v>
+      </c>
+      <c r="E14">
+        <v>0.99550000000000005</v>
+      </c>
+      <c r="H14" t="s">
+        <v>176</v>
+      </c>
+      <c r="I14" t="s">
+        <v>165</v>
+      </c>
+      <c r="J14">
+        <v>4.3185124826726443E-2</v>
+      </c>
+      <c r="K14" t="s">
+        <v>166</v>
+      </c>
+      <c r="L14" t="s">
+        <v>165</v>
+      </c>
+      <c r="P14" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>208</v>
+      </c>
+      <c r="R14" t="s">
+        <v>209</v>
+      </c>
+      <c r="U14" t="s">
+        <v>120</v>
+      </c>
+      <c r="V14" t="s">
+        <v>232</v>
+      </c>
+      <c r="W14" t="s">
+        <v>221</v>
+      </c>
+      <c r="X14" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D15">
+        <v>31.900000000000002</v>
+      </c>
+      <c r="E15">
+        <v>0.99826000000000004</v>
+      </c>
+      <c r="H15" t="s">
+        <v>177</v>
+      </c>
+      <c r="I15" t="s">
+        <v>165</v>
+      </c>
+      <c r="J15">
+        <v>5.1713650970698723E-2</v>
+      </c>
+      <c r="K15" t="s">
+        <v>166</v>
+      </c>
+      <c r="L15" t="s">
+        <v>165</v>
+      </c>
+      <c r="P15" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>210</v>
+      </c>
+      <c r="R15" t="s">
+        <v>209</v>
+      </c>
+      <c r="U15" t="s">
+        <v>120</v>
+      </c>
+      <c r="V15" t="s">
+        <v>233</v>
+      </c>
+      <c r="W15" t="s">
+        <v>221</v>
+      </c>
+      <c r="X15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D16">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E16">
+        <v>0.99951999999999996</v>
+      </c>
+      <c r="H16" t="s">
+        <v>178</v>
+      </c>
+      <c r="I16" t="s">
+        <v>165</v>
+      </c>
+      <c r="J16">
+        <v>1.2144714448026258E-2</v>
+      </c>
+      <c r="K16" t="s">
+        <v>166</v>
+      </c>
+      <c r="L16" t="s">
+        <v>165</v>
+      </c>
+      <c r="P16" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>211</v>
+      </c>
+      <c r="R16" t="s">
+        <v>209</v>
+      </c>
+      <c r="U16" t="s">
+        <v>120</v>
+      </c>
+      <c r="V16" t="s">
+        <v>234</v>
+      </c>
+      <c r="W16" t="s">
+        <v>221</v>
+      </c>
+      <c r="X16" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D17">
+        <v>41.800000000000004</v>
+      </c>
+      <c r="E17">
+        <v>0.99772000000000005</v>
+      </c>
+      <c r="H17" t="s">
+        <v>179</v>
+      </c>
+      <c r="I17" t="s">
+        <v>165</v>
+      </c>
+      <c r="J17">
+        <v>7.392672774910522E-2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>166</v>
+      </c>
+      <c r="L17" t="s">
+        <v>165</v>
+      </c>
+      <c r="P17" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>212</v>
+      </c>
+      <c r="R17" t="s">
+        <v>209</v>
+      </c>
+      <c r="U17" t="s">
+        <v>120</v>
+      </c>
+      <c r="V17" t="s">
+        <v>235</v>
+      </c>
+      <c r="W17" t="s">
+        <v>215</v>
+      </c>
+      <c r="X17" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D18">
+        <v>134.20000000000002</v>
+      </c>
+      <c r="E18">
+        <v>0.99268000000000001</v>
+      </c>
+      <c r="H18" t="s">
+        <v>180</v>
+      </c>
+      <c r="I18" t="s">
+        <v>165</v>
+      </c>
+      <c r="J18">
+        <v>3.633930313413767E-2</v>
+      </c>
+      <c r="K18" t="s">
+        <v>166</v>
+      </c>
+      <c r="L18" t="s">
+        <v>165</v>
+      </c>
+      <c r="P18" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>213</v>
+      </c>
+      <c r="R18" t="s">
+        <v>209</v>
+      </c>
+      <c r="U18" t="s">
+        <v>120</v>
+      </c>
+      <c r="V18" t="s">
+        <v>236</v>
+      </c>
+      <c r="W18" t="s">
+        <v>215</v>
+      </c>
+      <c r="X18" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D19">
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="E19">
+        <v>0.99982000000000004</v>
+      </c>
+      <c r="H19" t="s">
+        <v>181</v>
+      </c>
+      <c r="I19" t="s">
+        <v>165</v>
+      </c>
+      <c r="J19">
+        <v>3.5324533152767991E-2</v>
+      </c>
+      <c r="K19" t="s">
+        <v>166</v>
+      </c>
+      <c r="L19" t="s">
+        <v>165</v>
+      </c>
+      <c r="P19" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>214</v>
+      </c>
+      <c r="R19" t="s">
+        <v>209</v>
+      </c>
+      <c r="U19" t="s">
+        <v>120</v>
+      </c>
+      <c r="V19" t="s">
+        <v>237</v>
+      </c>
+      <c r="W19" t="s">
+        <v>215</v>
+      </c>
+      <c r="X19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D20">
+        <v>28.6</v>
+      </c>
+      <c r="E20">
+        <v>0.99843999999999999</v>
+      </c>
+      <c r="H20" t="s">
+        <v>182</v>
+      </c>
+      <c r="I20" t="s">
+        <v>165</v>
+      </c>
+      <c r="J20">
+        <v>3.5089155153095367E-2</v>
+      </c>
+      <c r="K20" t="s">
+        <v>166</v>
+      </c>
+      <c r="L20" t="s">
+        <v>165</v>
+      </c>
+      <c r="P20" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>215</v>
+      </c>
+      <c r="R20" t="s">
+        <v>209</v>
+      </c>
+      <c r="U20" t="s">
+        <v>120</v>
+      </c>
+      <c r="V20" t="s">
+        <v>238</v>
+      </c>
+      <c r="W20" t="s">
+        <v>239</v>
+      </c>
+      <c r="X20" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D21">
+        <v>50.6</v>
+      </c>
+      <c r="E21">
+        <v>0.99724000000000002</v>
+      </c>
+      <c r="H21" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" t="s">
+        <v>165</v>
+      </c>
+      <c r="J21">
+        <v>0.57933284097649596</v>
+      </c>
+      <c r="K21" t="s">
+        <v>166</v>
+      </c>
+      <c r="L21" t="s">
+        <v>165</v>
+      </c>
+      <c r="P21" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>216</v>
+      </c>
+      <c r="R21" t="s">
+        <v>209</v>
+      </c>
+      <c r="U21" t="s">
+        <v>120</v>
+      </c>
+      <c r="V21" t="s">
+        <v>240</v>
+      </c>
+      <c r="W21" t="s">
+        <v>239</v>
+      </c>
+      <c r="X21" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D22">
+        <v>19.8</v>
+      </c>
+      <c r="E22">
+        <v>0.99892000000000003</v>
+      </c>
+      <c r="H22" t="s">
+        <v>184</v>
+      </c>
+      <c r="I22" t="s">
+        <v>165</v>
+      </c>
+      <c r="J22">
+        <v>4.1164906764964301E-2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>166</v>
+      </c>
+      <c r="L22" t="s">
+        <v>165</v>
+      </c>
+      <c r="P22" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>217</v>
+      </c>
+      <c r="R22" t="s">
+        <v>209</v>
+      </c>
+      <c r="U22" t="s">
+        <v>120</v>
+      </c>
+      <c r="V22" t="s">
+        <v>241</v>
+      </c>
+      <c r="W22" t="s">
+        <v>239</v>
+      </c>
+      <c r="X22" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23">
+        <v>3.5749528668221644</v>
+      </c>
+      <c r="D23">
+        <v>457.6</v>
+      </c>
+      <c r="E23">
+        <v>0.97504000000000002</v>
+      </c>
+      <c r="H23" t="s">
+        <v>185</v>
+      </c>
+      <c r="I23" t="s">
+        <v>165</v>
+      </c>
+      <c r="J23">
+        <v>7.1779042823981773E-2</v>
+      </c>
+      <c r="K23" t="s">
+        <v>166</v>
+      </c>
+      <c r="L23" t="s">
+        <v>165</v>
+      </c>
+      <c r="P23" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>218</v>
+      </c>
+      <c r="R23" t="s">
+        <v>209</v>
+      </c>
+      <c r="U23" t="s">
+        <v>120</v>
+      </c>
+      <c r="V23" t="s">
+        <v>242</v>
+      </c>
+      <c r="W23" t="s">
+        <v>210</v>
+      </c>
+      <c r="X23" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24">
+        <v>3.5749528668221644</v>
+      </c>
+      <c r="D24">
+        <v>104.50000000000001</v>
+      </c>
+      <c r="E24">
+        <v>0.99429999999999996</v>
+      </c>
+      <c r="H24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I24" t="s">
+        <v>165</v>
+      </c>
+      <c r="J24">
+        <v>4.3185124826726443E-2</v>
+      </c>
+      <c r="K24" t="s">
+        <v>166</v>
+      </c>
+      <c r="L24" t="s">
+        <v>165</v>
+      </c>
+      <c r="P24" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>208</v>
+      </c>
+      <c r="R24" t="s">
+        <v>209</v>
+      </c>
+      <c r="U24" t="s">
+        <v>120</v>
+      </c>
+      <c r="V24" t="s">
+        <v>243</v>
+      </c>
+      <c r="W24" t="s">
+        <v>210</v>
+      </c>
+      <c r="X24" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D25">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="E25">
+        <v>0.99736000000000002</v>
+      </c>
+      <c r="H25" t="s">
+        <v>187</v>
+      </c>
+      <c r="I25" t="s">
+        <v>165</v>
+      </c>
+      <c r="J25">
+        <v>5.1713650970698723E-2</v>
+      </c>
+      <c r="K25" t="s">
+        <v>166</v>
+      </c>
+      <c r="L25" t="s">
+        <v>165</v>
+      </c>
+      <c r="P25" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>210</v>
+      </c>
+      <c r="R25" t="s">
+        <v>209</v>
+      </c>
+      <c r="U25" t="s">
+        <v>120</v>
+      </c>
+      <c r="V25" t="s">
+        <v>244</v>
+      </c>
+      <c r="W25" t="s">
+        <v>210</v>
+      </c>
+      <c r="X25" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26">
+        <v>3.5749528668221644</v>
+      </c>
+      <c r="D26">
+        <v>18.700000000000003</v>
+      </c>
+      <c r="E26">
+        <v>0.99897999999999998</v>
+      </c>
+      <c r="H26" t="s">
+        <v>188</v>
+      </c>
+      <c r="I26" t="s">
+        <v>165</v>
+      </c>
+      <c r="J26">
+        <v>1.2144714448026258E-2</v>
+      </c>
+      <c r="K26" t="s">
+        <v>166</v>
+      </c>
+      <c r="L26" t="s">
+        <v>165</v>
+      </c>
+      <c r="P26" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>211</v>
+      </c>
+      <c r="R26" t="s">
+        <v>209</v>
+      </c>
+      <c r="U26" t="s">
+        <v>120</v>
+      </c>
+      <c r="V26" t="s">
+        <v>245</v>
+      </c>
+      <c r="W26" t="s">
+        <v>246</v>
+      </c>
+      <c r="X26" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27">
+        <v>8.937382167055409</v>
+      </c>
+      <c r="D27">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E27">
+        <v>0.99987999999999999</v>
+      </c>
+      <c r="H27" t="s">
+        <v>189</v>
+      </c>
+      <c r="I27" t="s">
+        <v>165</v>
+      </c>
+      <c r="J27">
+        <v>7.392672774910522E-2</v>
+      </c>
+      <c r="K27" t="s">
+        <v>166</v>
+      </c>
+      <c r="L27" t="s">
+        <v>165</v>
+      </c>
+      <c r="P27" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>212</v>
+      </c>
+      <c r="R27" t="s">
+        <v>209</v>
+      </c>
+      <c r="U27" t="s">
+        <v>120</v>
+      </c>
+      <c r="V27" t="s">
+        <v>247</v>
+      </c>
+      <c r="W27" t="s">
+        <v>246</v>
+      </c>
+      <c r="X27" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D28">
+        <v>72.600000000000009</v>
+      </c>
+      <c r="E28">
+        <v>0.99604000000000004</v>
+      </c>
+      <c r="H28" t="s">
+        <v>190</v>
+      </c>
+      <c r="I28" t="s">
+        <v>165</v>
+      </c>
+      <c r="J28">
+        <v>3.633930313413767E-2</v>
+      </c>
+      <c r="K28" t="s">
+        <v>166</v>
+      </c>
+      <c r="L28" t="s">
+        <v>165</v>
+      </c>
+      <c r="P28" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>213</v>
+      </c>
+      <c r="R28" t="s">
+        <v>209</v>
+      </c>
+      <c r="U28" t="s">
+        <v>120</v>
+      </c>
+      <c r="V28" t="s">
+        <v>248</v>
+      </c>
+      <c r="W28" t="s">
+        <v>246</v>
+      </c>
+      <c r="X28" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D29">
+        <v>113.30000000000001</v>
+      </c>
+      <c r="E29">
+        <v>0.99382000000000004</v>
+      </c>
+      <c r="H29" t="s">
+        <v>191</v>
+      </c>
+      <c r="I29" t="s">
+        <v>165</v>
+      </c>
+      <c r="J29">
+        <v>3.5324533152767991E-2</v>
+      </c>
+      <c r="K29" t="s">
+        <v>166</v>
+      </c>
+      <c r="L29" t="s">
+        <v>165</v>
+      </c>
+      <c r="P29" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>214</v>
+      </c>
+      <c r="R29" t="s">
+        <v>209</v>
+      </c>
+      <c r="U29" t="s">
+        <v>120</v>
+      </c>
+      <c r="V29" t="s">
+        <v>249</v>
+      </c>
+      <c r="W29" t="s">
+        <v>212</v>
+      </c>
+      <c r="X29" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D30">
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="E30">
+        <v>0.99963999999999997</v>
+      </c>
+      <c r="H30" t="s">
+        <v>192</v>
+      </c>
+      <c r="I30" t="s">
+        <v>165</v>
+      </c>
+      <c r="J30">
+        <v>3.5089155153095367E-2</v>
+      </c>
+      <c r="K30" t="s">
+        <v>166</v>
+      </c>
+      <c r="L30" t="s">
+        <v>165</v>
+      </c>
+      <c r="P30" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>215</v>
+      </c>
+      <c r="R30" t="s">
+        <v>209</v>
+      </c>
+      <c r="U30" t="s">
+        <v>120</v>
+      </c>
+      <c r="V30" t="s">
+        <v>250</v>
+      </c>
+      <c r="W30" t="s">
+        <v>212</v>
+      </c>
+      <c r="X30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="31" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>151</v>
+      </c>
+      <c r="C31">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D31">
+        <v>12.100000000000001</v>
+      </c>
+      <c r="E31">
+        <v>0.99934000000000001</v>
+      </c>
+      <c r="H31" t="s">
+        <v>193</v>
+      </c>
+      <c r="I31" t="s">
+        <v>165</v>
+      </c>
+      <c r="J31">
+        <v>0.57933284097649596</v>
+      </c>
+      <c r="K31" t="s">
+        <v>166</v>
+      </c>
+      <c r="L31" t="s">
+        <v>165</v>
+      </c>
+      <c r="P31" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>216</v>
+      </c>
+      <c r="R31" t="s">
+        <v>209</v>
+      </c>
+      <c r="U31" t="s">
+        <v>120</v>
+      </c>
+      <c r="V31" t="s">
+        <v>251</v>
+      </c>
+      <c r="W31" t="s">
+        <v>212</v>
+      </c>
+      <c r="X31" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="32" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D32">
+        <v>447.70000000000005</v>
+      </c>
+      <c r="E32">
+        <v>0.97558</v>
+      </c>
+      <c r="H32" t="s">
+        <v>194</v>
+      </c>
+      <c r="I32" t="s">
+        <v>165</v>
+      </c>
+      <c r="J32">
+        <v>4.1164906764964301E-2</v>
+      </c>
+      <c r="K32" t="s">
+        <v>166</v>
+      </c>
+      <c r="L32" t="s">
+        <v>165</v>
+      </c>
+      <c r="P32" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>217</v>
+      </c>
+      <c r="R32" t="s">
+        <v>209</v>
+      </c>
+      <c r="U32" t="s">
+        <v>120</v>
+      </c>
+      <c r="V32" t="s">
+        <v>252</v>
+      </c>
+      <c r="W32" t="s">
+        <v>253</v>
+      </c>
+      <c r="X32" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D33">
+        <v>177.10000000000002</v>
+      </c>
+      <c r="E33">
+        <v>0.99034</v>
+      </c>
+      <c r="H33" t="s">
+        <v>195</v>
+      </c>
+      <c r="I33" t="s">
+        <v>165</v>
+      </c>
+      <c r="J33">
+        <v>7.1779042823981773E-2</v>
+      </c>
+      <c r="K33" t="s">
+        <v>166</v>
+      </c>
+      <c r="L33" t="s">
+        <v>165</v>
+      </c>
+      <c r="P33" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>218</v>
+      </c>
+      <c r="R33" t="s">
+        <v>209</v>
+      </c>
+      <c r="U33" t="s">
+        <v>120</v>
+      </c>
+      <c r="V33" t="s">
+        <v>254</v>
+      </c>
+      <c r="W33" t="s">
+        <v>253</v>
+      </c>
+      <c r="X33" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D34">
+        <v>79.2</v>
+      </c>
+      <c r="E34">
+        <v>0.99568000000000001</v>
+      </c>
+      <c r="H34" t="s">
+        <v>196</v>
+      </c>
+      <c r="I34" t="s">
+        <v>165</v>
+      </c>
+      <c r="J34">
+        <v>4.3185124826726443E-2</v>
+      </c>
+      <c r="K34" t="s">
+        <v>166</v>
+      </c>
+      <c r="L34" t="s">
+        <v>165</v>
+      </c>
+      <c r="P34" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>208</v>
+      </c>
+      <c r="R34" t="s">
+        <v>209</v>
+      </c>
+      <c r="U34" t="s">
+        <v>120</v>
+      </c>
+      <c r="V34" t="s">
+        <v>255</v>
+      </c>
+      <c r="W34" t="s">
+        <v>253</v>
+      </c>
+      <c r="X34" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D35">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E35">
+        <v>0.99975999999999998</v>
+      </c>
+      <c r="H35" t="s">
+        <v>197</v>
+      </c>
+      <c r="I35" t="s">
+        <v>165</v>
+      </c>
+      <c r="J35">
+        <v>5.1713650970698723E-2</v>
+      </c>
+      <c r="K35" t="s">
+        <v>166</v>
+      </c>
+      <c r="L35" t="s">
+        <v>165</v>
+      </c>
+      <c r="P35" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>210</v>
+      </c>
+      <c r="R35" t="s">
+        <v>209</v>
+      </c>
+      <c r="U35" t="s">
+        <v>120</v>
+      </c>
+      <c r="V35" t="s">
+        <v>256</v>
+      </c>
+      <c r="W35" t="s">
+        <v>257</v>
+      </c>
+      <c r="X35" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D36">
+        <v>14.3</v>
+      </c>
+      <c r="E36">
+        <v>0.99922</v>
+      </c>
+      <c r="H36" t="s">
+        <v>198</v>
+      </c>
+      <c r="I36" t="s">
+        <v>165</v>
+      </c>
+      <c r="J36">
+        <v>1.2144714448026258E-2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>166</v>
+      </c>
+      <c r="L36" t="s">
+        <v>165</v>
+      </c>
+      <c r="P36" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>211</v>
+      </c>
+      <c r="R36" t="s">
+        <v>209</v>
+      </c>
+      <c r="U36" t="s">
+        <v>120</v>
+      </c>
+      <c r="V36" t="s">
+        <v>258</v>
+      </c>
+      <c r="W36" t="s">
+        <v>257</v>
+      </c>
+      <c r="X36" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D37">
+        <v>130.9</v>
+      </c>
+      <c r="E37">
+        <v>0.99285999999999996</v>
+      </c>
+      <c r="H37" t="s">
+        <v>199</v>
+      </c>
+      <c r="I37" t="s">
+        <v>165</v>
+      </c>
+      <c r="J37">
+        <v>7.392672774910522E-2</v>
+      </c>
+      <c r="K37" t="s">
+        <v>166</v>
+      </c>
+      <c r="L37" t="s">
+        <v>165</v>
+      </c>
+      <c r="P37" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>212</v>
+      </c>
+      <c r="R37" t="s">
+        <v>209</v>
+      </c>
+      <c r="U37" t="s">
+        <v>120</v>
+      </c>
+      <c r="V37" t="s">
+        <v>259</v>
+      </c>
+      <c r="W37" t="s">
+        <v>257</v>
+      </c>
+      <c r="X37" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38">
+        <v>0.98311203837609484</v>
+      </c>
+      <c r="D38">
+        <v>25.3</v>
+      </c>
+      <c r="E38">
+        <v>0.99861999999999995</v>
+      </c>
+      <c r="H38" t="s">
+        <v>200</v>
+      </c>
+      <c r="I38" t="s">
+        <v>165</v>
+      </c>
+      <c r="J38">
+        <v>3.633930313413767E-2</v>
+      </c>
+      <c r="K38" t="s">
+        <v>166</v>
+      </c>
+      <c r="L38" t="s">
+        <v>165</v>
+      </c>
+      <c r="P38" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>213</v>
+      </c>
+      <c r="R38" t="s">
+        <v>209</v>
+      </c>
+      <c r="U38" t="s">
+        <v>120</v>
+      </c>
+      <c r="V38" t="s">
+        <v>260</v>
+      </c>
+      <c r="W38" t="s">
+        <v>221</v>
+      </c>
+      <c r="X38" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>159</v>
+      </c>
+      <c r="C39">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D39">
+        <v>110.00000000000001</v>
+      </c>
+      <c r="E39">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="H39" t="s">
+        <v>201</v>
+      </c>
+      <c r="I39" t="s">
+        <v>165</v>
+      </c>
+      <c r="J39">
+        <v>3.5324533152767991E-2</v>
+      </c>
+      <c r="K39" t="s">
+        <v>166</v>
+      </c>
+      <c r="L39" t="s">
+        <v>165</v>
+      </c>
+      <c r="P39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>214</v>
+      </c>
+      <c r="R39" t="s">
+        <v>209</v>
+      </c>
+      <c r="U39" t="s">
+        <v>120</v>
+      </c>
+      <c r="V39" t="s">
+        <v>261</v>
+      </c>
+      <c r="W39" t="s">
+        <v>221</v>
+      </c>
+      <c r="X39" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="H40" t="s">
+        <v>202</v>
+      </c>
+      <c r="I40" t="s">
+        <v>165</v>
+      </c>
+      <c r="J40">
+        <v>3.5089155153095367E-2</v>
+      </c>
+      <c r="K40" t="s">
+        <v>166</v>
+      </c>
+      <c r="L40" t="s">
+        <v>165</v>
+      </c>
+      <c r="P40" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>215</v>
+      </c>
+      <c r="R40" t="s">
+        <v>209</v>
+      </c>
+      <c r="U40" t="s">
+        <v>120</v>
+      </c>
+      <c r="V40" t="s">
+        <v>262</v>
+      </c>
+      <c r="W40" t="s">
+        <v>217</v>
+      </c>
+      <c r="X40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="H41" t="s">
+        <v>203</v>
+      </c>
+      <c r="I41" t="s">
+        <v>165</v>
+      </c>
+      <c r="J41">
+        <v>0.57933284097649596</v>
+      </c>
+      <c r="K41" t="s">
+        <v>166</v>
+      </c>
+      <c r="L41" t="s">
+        <v>165</v>
+      </c>
+      <c r="P41" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>216</v>
+      </c>
+      <c r="R41" t="s">
+        <v>209</v>
+      </c>
+      <c r="U41" t="s">
+        <v>120</v>
+      </c>
+      <c r="V41" t="s">
+        <v>263</v>
+      </c>
+      <c r="W41" t="s">
+        <v>217</v>
+      </c>
+      <c r="X41" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="H42" t="s">
+        <v>204</v>
+      </c>
+      <c r="I42" t="s">
+        <v>165</v>
+      </c>
+      <c r="J42">
+        <v>4.1164906764964301E-2</v>
+      </c>
+      <c r="K42" t="s">
+        <v>166</v>
+      </c>
+      <c r="L42" t="s">
+        <v>165</v>
+      </c>
+      <c r="P42" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>217</v>
+      </c>
+      <c r="R42" t="s">
+        <v>209</v>
+      </c>
+      <c r="U42" t="s">
+        <v>120</v>
+      </c>
+      <c r="V42" t="s">
+        <v>264</v>
+      </c>
+      <c r="W42" t="s">
+        <v>216</v>
+      </c>
+      <c r="X42" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="H43" t="s">
+        <v>205</v>
+      </c>
+      <c r="I43" t="s">
+        <v>165</v>
+      </c>
+      <c r="J43">
+        <v>7.1779042823981773E-2</v>
+      </c>
+      <c r="K43" t="s">
+        <v>166</v>
+      </c>
+      <c r="L43" t="s">
+        <v>165</v>
+      </c>
+      <c r="P43" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>218</v>
+      </c>
+      <c r="R43" t="s">
+        <v>209</v>
+      </c>
+      <c r="U43" t="s">
+        <v>120</v>
+      </c>
+      <c r="V43" t="s">
+        <v>265</v>
+      </c>
+      <c r="W43" t="s">
+        <v>216</v>
+      </c>
+      <c r="X43" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="U44" t="s">
+        <v>120</v>
+      </c>
+      <c r="V44" t="s">
+        <v>266</v>
+      </c>
+      <c r="W44" t="s">
+        <v>267</v>
+      </c>
+      <c r="X44" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="U45" t="s">
+        <v>120</v>
+      </c>
+      <c r="V45" t="s">
+        <v>268</v>
+      </c>
+      <c r="W45" t="s">
+        <v>267</v>
+      </c>
+      <c r="X45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="U46" t="s">
+        <v>120</v>
+      </c>
+      <c r="V46" t="s">
+        <v>269</v>
+      </c>
+      <c r="W46" t="s">
+        <v>212</v>
+      </c>
+      <c r="X46" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="U47" t="s">
+        <v>120</v>
+      </c>
+      <c r="V47" t="s">
+        <v>270</v>
+      </c>
+      <c r="W47" t="s">
+        <v>212</v>
+      </c>
+      <c r="X47" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="U48" t="s">
+        <v>120</v>
+      </c>
+      <c r="V48" t="s">
+        <v>271</v>
+      </c>
+      <c r="W48" t="s">
+        <v>211</v>
+      </c>
+      <c r="X48" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="49" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U49" t="s">
+        <v>120</v>
+      </c>
+      <c r="V49" t="s">
+        <v>272</v>
+      </c>
+      <c r="W49" t="s">
+        <v>211</v>
+      </c>
+      <c r="X49" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U50" t="s">
+        <v>120</v>
+      </c>
+      <c r="V50" t="s">
+        <v>273</v>
+      </c>
+      <c r="W50" t="s">
+        <v>213</v>
+      </c>
+      <c r="X50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="51" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U51" t="s">
+        <v>120</v>
+      </c>
+      <c r="V51" t="s">
+        <v>274</v>
+      </c>
+      <c r="W51" t="s">
+        <v>213</v>
+      </c>
+      <c r="X51" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="52" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U52" t="s">
+        <v>120</v>
+      </c>
+      <c r="V52" t="s">
+        <v>275</v>
+      </c>
+      <c r="W52" t="s">
+        <v>276</v>
+      </c>
+      <c r="X52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="53" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V53" t="s">
+        <v>277</v>
+      </c>
+      <c r="W53" t="s">
+        <v>276</v>
+      </c>
+      <c r="X53" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="54" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U54" t="s">
+        <v>120</v>
+      </c>
+      <c r="V54" t="s">
+        <v>278</v>
+      </c>
+      <c r="W54" t="s">
+        <v>218</v>
+      </c>
+      <c r="X54" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="55" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U55" t="s">
+        <v>120</v>
+      </c>
+      <c r="V55" t="s">
+        <v>279</v>
+      </c>
+      <c r="W55" t="s">
+        <v>218</v>
+      </c>
+      <c r="X55" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="56" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U56" t="s">
+        <v>120</v>
+      </c>
+      <c r="V56" t="s">
+        <v>280</v>
+      </c>
+      <c r="W56" t="s">
+        <v>215</v>
+      </c>
+      <c r="X56" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U57" t="s">
+        <v>120</v>
+      </c>
+      <c r="V57" t="s">
+        <v>281</v>
+      </c>
+      <c r="W57" t="s">
+        <v>215</v>
+      </c>
+      <c r="X57" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="58" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U58" t="s">
+        <v>120</v>
+      </c>
+      <c r="V58" t="s">
+        <v>282</v>
+      </c>
+      <c r="W58" t="s">
+        <v>257</v>
+      </c>
+      <c r="X58" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="59" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U59" t="s">
+        <v>120</v>
+      </c>
+      <c r="V59" t="s">
+        <v>283</v>
+      </c>
+      <c r="W59" t="s">
+        <v>257</v>
+      </c>
+      <c r="X59" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="60" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U60" t="s">
+        <v>120</v>
+      </c>
+      <c r="V60" t="s">
+        <v>284</v>
+      </c>
+      <c r="W60" t="s">
+        <v>285</v>
+      </c>
+      <c r="X60" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="61" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U61" t="s">
+        <v>120</v>
+      </c>
+      <c r="V61" t="s">
+        <v>286</v>
+      </c>
+      <c r="W61" t="s">
+        <v>285</v>
+      </c>
+      <c r="X61" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="62" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U62" t="s">
+        <v>120</v>
+      </c>
+      <c r="V62" t="s">
+        <v>287</v>
+      </c>
+      <c r="W62" t="s">
+        <v>288</v>
+      </c>
+      <c r="X62" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="63" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U63" t="s">
+        <v>120</v>
+      </c>
+      <c r="V63" t="s">
+        <v>289</v>
+      </c>
+      <c r="W63" t="s">
+        <v>288</v>
+      </c>
+      <c r="X63" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="64" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U64" t="s">
+        <v>120</v>
+      </c>
+      <c r="V64" t="s">
+        <v>290</v>
+      </c>
+      <c r="W64" t="s">
+        <v>291</v>
+      </c>
+      <c r="X64" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="65" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U65" t="s">
+        <v>120</v>
+      </c>
+      <c r="V65" t="s">
+        <v>292</v>
+      </c>
+      <c r="W65" t="s">
+        <v>291</v>
+      </c>
+      <c r="X65" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U66" t="s">
+        <v>120</v>
+      </c>
+      <c r="V66" t="s">
+        <v>293</v>
+      </c>
+      <c r="W66" t="s">
+        <v>294</v>
+      </c>
+      <c r="X66" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="67" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U67" t="s">
+        <v>120</v>
+      </c>
+      <c r="V67" t="s">
+        <v>295</v>
+      </c>
+      <c r="W67" t="s">
+        <v>294</v>
+      </c>
+      <c r="X67" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="68" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U68" t="s">
+        <v>120</v>
+      </c>
+      <c r="V68" t="s">
+        <v>296</v>
+      </c>
+      <c r="W68" t="s">
+        <v>297</v>
+      </c>
+      <c r="X68" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="69" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U69" t="s">
+        <v>120</v>
+      </c>
+      <c r="V69" t="s">
+        <v>298</v>
+      </c>
+      <c r="W69" t="s">
+        <v>297</v>
+      </c>
+      <c r="X69" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="70" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U70" t="s">
+        <v>120</v>
+      </c>
+      <c r="V70" t="s">
+        <v>299</v>
+      </c>
+      <c r="W70" t="s">
+        <v>300</v>
+      </c>
+      <c r="X70" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="71" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U71" t="s">
+        <v>120</v>
+      </c>
+      <c r="V71" t="s">
+        <v>301</v>
+      </c>
+      <c r="W71" t="s">
+        <v>300</v>
+      </c>
+      <c r="X71" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U72" t="s">
+        <v>120</v>
+      </c>
+      <c r="V72" t="s">
+        <v>302</v>
+      </c>
+      <c r="W72" t="s">
+        <v>239</v>
+      </c>
+      <c r="X72" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="73" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U73" t="s">
+        <v>120</v>
+      </c>
+      <c r="V73" t="s">
+        <v>303</v>
+      </c>
+      <c r="W73" t="s">
+        <v>239</v>
+      </c>
+      <c r="X73" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U74" t="s">
+        <v>120</v>
+      </c>
+      <c r="V74" t="s">
+        <v>304</v>
+      </c>
+      <c r="W74" t="s">
+        <v>210</v>
+      </c>
+      <c r="X74" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="75" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U75" t="s">
+        <v>120</v>
+      </c>
+      <c r="V75" t="s">
+        <v>305</v>
+      </c>
+      <c r="W75" t="s">
+        <v>210</v>
+      </c>
+      <c r="X75" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="76" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U76" t="s">
+        <v>120</v>
+      </c>
+      <c r="V76" t="s">
+        <v>306</v>
+      </c>
+      <c r="W76" t="s">
+        <v>246</v>
+      </c>
+      <c r="X76" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="77" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U77" t="s">
+        <v>120</v>
+      </c>
+      <c r="V77" t="s">
+        <v>307</v>
+      </c>
+      <c r="W77" t="s">
+        <v>246</v>
+      </c>
+      <c r="X77" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="78" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U78" t="s">
+        <v>120</v>
+      </c>
+      <c r="V78" t="s">
+        <v>308</v>
+      </c>
+      <c r="W78" t="s">
+        <v>253</v>
+      </c>
+      <c r="X78" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="79" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U79" t="s">
+        <v>120</v>
+      </c>
+      <c r="V79" t="s">
+        <v>309</v>
+      </c>
+      <c r="W79" t="s">
+        <v>253</v>
+      </c>
+      <c r="X79" t="s">
+        <v>222</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26CB159B-A929-4386-8CD3-4249F9D23578}">
+  <dimension ref="B9:L26"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B11">
+        <v>2030</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J11" t="s">
+        <v>108</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B12">
+        <v>2030</v>
+      </c>
+      <c r="C12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12">
+        <v>0.67</v>
+      </c>
+      <c r="F12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H12" t="s">
+        <v>107</v>
+      </c>
+      <c r="I12" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J12" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B13">
+        <v>2030</v>
+      </c>
+      <c r="C13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J13" t="s">
+        <v>108</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B14">
+        <v>2030</v>
+      </c>
+      <c r="C14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14">
+        <v>1.67</v>
+      </c>
+      <c r="F14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J14" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B15">
+        <v>2030</v>
+      </c>
+      <c r="C15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15">
+        <v>2.67</v>
+      </c>
+      <c r="F15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J15" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B16">
+        <v>2030</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16">
+        <v>3.67</v>
+      </c>
+      <c r="F16" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J16" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B17">
+        <v>2030</v>
+      </c>
+      <c r="C17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17">
+        <v>28</v>
+      </c>
+      <c r="F17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J17" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B18">
+        <v>2030</v>
+      </c>
+      <c r="C18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18">
+        <v>8.07</v>
+      </c>
+      <c r="F18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H18" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J18" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B19">
+        <v>2030</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19">
+        <v>6.6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J19" t="s">
+        <v>108</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B20">
+        <v>2030</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" t="s">
+        <v>106</v>
+      </c>
+      <c r="H20" t="s">
+        <v>107</v>
+      </c>
+      <c r="I20" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J20" t="s">
+        <v>108</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B21">
+        <v>2030</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21">
+        <v>3.67</v>
+      </c>
+      <c r="F21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J21" t="s">
+        <v>108</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B22">
+        <v>2030</v>
+      </c>
+      <c r="C22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22">
+        <v>11.11</v>
+      </c>
+      <c r="F22" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" t="s">
+        <v>106</v>
+      </c>
+      <c r="H22" t="s">
+        <v>107</v>
+      </c>
+      <c r="I22" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B23">
+        <v>2030</v>
+      </c>
+      <c r="C23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23">
+        <v>24.44</v>
+      </c>
+      <c r="F23" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J23" t="s">
+        <v>108</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B24">
+        <v>2030</v>
+      </c>
+      <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>105</v>
+      </c>
+      <c r="G24" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" t="s">
+        <v>107</v>
+      </c>
+      <c r="I24" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J24" t="s">
+        <v>108</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B25">
+        <v>2030</v>
+      </c>
+      <c r="C25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25">
+        <v>33.33</v>
+      </c>
+      <c r="F25" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" t="s">
+        <v>107</v>
+      </c>
+      <c r="I25" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J25" t="s">
+        <v>108</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B26">
+        <v>2030</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26">
+        <v>11.11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" t="s">
+        <v>107</v>
+      </c>
+      <c r="I26" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J26" t="s">
+        <v>108</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1606,7 +4799,7 @@
     <col min="33" max="33" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.265625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1711,7 +4904,7 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1958,7 +5151,7 @@
         <v>0.22132714596479999</v>
       </c>
       <c r="AF10" t="s">
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="AG10" t="s">
         <v>23</v>
@@ -1971,7 +5164,7 @@
         <f>VLOOKUP(AG10,$F$3:$J$11,2,FALSE)</f>
         <v>0.10772396938709886</v>
       </c>
-      <c r="AJ10">
+      <c r="AJ10" s="12">
         <f>AI10*$AD$1</f>
         <v>2.1544793877419772E-2</v>
       </c>
@@ -1984,7 +5177,7 @@
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3">
         <v>0.11415525114155252</v>
@@ -2312,3197 +5505,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877A6333-0464-4EC5-991B-E1B8D5F11AB4}">
-  <dimension ref="B2:AF79"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>159</v>
-      </c>
-      <c r="P2" t="s">
-        <v>205</v>
-      </c>
-      <c r="U2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J3" t="s">
-        <v>161</v>
-      </c>
-      <c r="K3" t="s">
-        <v>162</v>
-      </c>
-      <c r="L3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>160</v>
-      </c>
-      <c r="R3" t="s">
-        <v>206</v>
-      </c>
-      <c r="U3" t="s">
-        <v>218</v>
-      </c>
-      <c r="V3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W3" t="s">
-        <v>160</v>
-      </c>
-      <c r="X3" t="s">
-        <v>206</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4">
-        <v>3.5749528668221644</v>
-      </c>
-      <c r="D4">
-        <v>433.40000000000003</v>
-      </c>
-      <c r="E4">
-        <v>0.97636000000000001</v>
-      </c>
-      <c r="H4" t="s">
-        <v>163</v>
-      </c>
-      <c r="I4" t="s">
-        <v>164</v>
-      </c>
-      <c r="J4">
-        <v>4.3185124826726443E-2</v>
-      </c>
-      <c r="K4" t="s">
-        <v>165</v>
-      </c>
-      <c r="L4" t="s">
-        <v>164</v>
-      </c>
-      <c r="P4" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>207</v>
-      </c>
-      <c r="R4" t="s">
-        <v>208</v>
-      </c>
-      <c r="U4" t="s">
-        <v>119</v>
-      </c>
-      <c r="V4" t="s">
-        <v>219</v>
-      </c>
-      <c r="W4" t="s">
-        <v>220</v>
-      </c>
-      <c r="X4" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>160</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>310</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>312</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>313</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5">
-        <v>3.5749528668221644</v>
-      </c>
-      <c r="D5">
-        <v>218.9</v>
-      </c>
-      <c r="E5">
-        <v>0.98806000000000005</v>
-      </c>
-      <c r="H5" t="s">
-        <v>166</v>
-      </c>
-      <c r="I5" t="s">
-        <v>164</v>
-      </c>
-      <c r="J5">
-        <v>5.1713650970698723E-2</v>
-      </c>
-      <c r="K5" t="s">
-        <v>165</v>
-      </c>
-      <c r="L5" t="s">
-        <v>164</v>
-      </c>
-      <c r="P5" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>209</v>
-      </c>
-      <c r="R5" t="s">
-        <v>208</v>
-      </c>
-      <c r="U5" t="s">
-        <v>119</v>
-      </c>
-      <c r="V5" t="s">
-        <v>222</v>
-      </c>
-      <c r="W5" t="s">
-        <v>220</v>
-      </c>
-      <c r="X5" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>309</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>311</v>
-      </c>
-      <c r="AC5">
-        <v>2</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D6">
-        <v>136.4</v>
-      </c>
-      <c r="E6">
-        <v>0.99256</v>
-      </c>
-      <c r="H6" t="s">
-        <v>167</v>
-      </c>
-      <c r="I6" t="s">
-        <v>164</v>
-      </c>
-      <c r="J6">
-        <v>1.2144714448026258E-2</v>
-      </c>
-      <c r="K6" t="s">
-        <v>165</v>
-      </c>
-      <c r="L6" t="s">
-        <v>164</v>
-      </c>
-      <c r="P6" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>210</v>
-      </c>
-      <c r="R6" t="s">
-        <v>208</v>
-      </c>
-      <c r="U6" t="s">
-        <v>119</v>
-      </c>
-      <c r="V6" t="s">
-        <v>223</v>
-      </c>
-      <c r="W6" t="s">
-        <v>220</v>
-      </c>
-      <c r="X6" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>309</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD6">
-        <v>2</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D7">
-        <v>30.800000000000004</v>
-      </c>
-      <c r="E7">
-        <v>0.99831999999999999</v>
-      </c>
-      <c r="H7" t="s">
-        <v>168</v>
-      </c>
-      <c r="I7" t="s">
-        <v>164</v>
-      </c>
-      <c r="J7">
-        <v>7.392672774910522E-2</v>
-      </c>
-      <c r="K7" t="s">
-        <v>165</v>
-      </c>
-      <c r="L7" t="s">
-        <v>164</v>
-      </c>
-      <c r="P7" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>211</v>
-      </c>
-      <c r="R7" t="s">
-        <v>208</v>
-      </c>
-      <c r="U7" t="s">
-        <v>119</v>
-      </c>
-      <c r="V7" t="s">
-        <v>224</v>
-      </c>
-      <c r="W7" t="s">
-        <v>220</v>
-      </c>
-      <c r="X7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D8">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E8">
-        <v>0.99994000000000005</v>
-      </c>
-      <c r="H8" t="s">
-        <v>169</v>
-      </c>
-      <c r="I8" t="s">
-        <v>164</v>
-      </c>
-      <c r="J8">
-        <v>3.633930313413767E-2</v>
-      </c>
-      <c r="K8" t="s">
-        <v>165</v>
-      </c>
-      <c r="L8" t="s">
-        <v>164</v>
-      </c>
-      <c r="P8" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>212</v>
-      </c>
-      <c r="R8" t="s">
-        <v>208</v>
-      </c>
-      <c r="U8" t="s">
-        <v>119</v>
-      </c>
-      <c r="V8" t="s">
-        <v>225</v>
-      </c>
-      <c r="W8" t="s">
-        <v>220</v>
-      </c>
-      <c r="X8" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D9">
-        <v>7.7000000000000011</v>
-      </c>
-      <c r="E9">
-        <v>0.99958000000000002</v>
-      </c>
-      <c r="H9" t="s">
-        <v>170</v>
-      </c>
-      <c r="I9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J9">
-        <v>3.5324533152767991E-2</v>
-      </c>
-      <c r="K9" t="s">
-        <v>165</v>
-      </c>
-      <c r="L9" t="s">
-        <v>164</v>
-      </c>
-      <c r="P9" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>213</v>
-      </c>
-      <c r="R9" t="s">
-        <v>208</v>
-      </c>
-      <c r="U9" t="s">
-        <v>119</v>
-      </c>
-      <c r="V9" t="s">
-        <v>226</v>
-      </c>
-      <c r="W9" t="s">
-        <v>220</v>
-      </c>
-      <c r="X9" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D10">
-        <v>26.400000000000002</v>
-      </c>
-      <c r="E10">
-        <v>0.99856</v>
-      </c>
-      <c r="H10" t="s">
-        <v>171</v>
-      </c>
-      <c r="I10" t="s">
-        <v>164</v>
-      </c>
-      <c r="J10">
-        <v>3.5089155153095367E-2</v>
-      </c>
-      <c r="K10" t="s">
-        <v>165</v>
-      </c>
-      <c r="L10" t="s">
-        <v>164</v>
-      </c>
-      <c r="P10" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>214</v>
-      </c>
-      <c r="R10" t="s">
-        <v>208</v>
-      </c>
-      <c r="U10" t="s">
-        <v>119</v>
-      </c>
-      <c r="V10" t="s">
-        <v>227</v>
-      </c>
-      <c r="W10" t="s">
-        <v>220</v>
-      </c>
-      <c r="X10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D11">
-        <v>22</v>
-      </c>
-      <c r="E11">
-        <v>0.99880000000000002</v>
-      </c>
-      <c r="H11" t="s">
-        <v>172</v>
-      </c>
-      <c r="I11" t="s">
-        <v>164</v>
-      </c>
-      <c r="J11">
-        <v>0.57933284097649596</v>
-      </c>
-      <c r="K11" t="s">
-        <v>165</v>
-      </c>
-      <c r="L11" t="s">
-        <v>164</v>
-      </c>
-      <c r="P11" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>215</v>
-      </c>
-      <c r="R11" t="s">
-        <v>208</v>
-      </c>
-      <c r="U11" t="s">
-        <v>119</v>
-      </c>
-      <c r="V11" t="s">
-        <v>228</v>
-      </c>
-      <c r="W11" t="s">
-        <v>220</v>
-      </c>
-      <c r="X11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D12">
-        <v>221.10000000000002</v>
-      </c>
-      <c r="E12">
-        <v>0.98794000000000004</v>
-      </c>
-      <c r="H12" t="s">
-        <v>173</v>
-      </c>
-      <c r="I12" t="s">
-        <v>164</v>
-      </c>
-      <c r="J12">
-        <v>4.1164906764964301E-2</v>
-      </c>
-      <c r="K12" t="s">
-        <v>165</v>
-      </c>
-      <c r="L12" t="s">
-        <v>164</v>
-      </c>
-      <c r="P12" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>216</v>
-      </c>
-      <c r="R12" t="s">
-        <v>208</v>
-      </c>
-      <c r="U12" t="s">
-        <v>119</v>
-      </c>
-      <c r="V12" t="s">
-        <v>229</v>
-      </c>
-      <c r="W12" t="s">
-        <v>220</v>
-      </c>
-      <c r="X12" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13">
-        <v>3.5749528668221644</v>
-      </c>
-      <c r="D13">
-        <v>248.60000000000002</v>
-      </c>
-      <c r="E13">
-        <v>0.98643999999999998</v>
-      </c>
-      <c r="H13" t="s">
-        <v>174</v>
-      </c>
-      <c r="I13" t="s">
-        <v>164</v>
-      </c>
-      <c r="J13">
-        <v>7.1779042823981773E-2</v>
-      </c>
-      <c r="K13" t="s">
-        <v>165</v>
-      </c>
-      <c r="L13" t="s">
-        <v>164</v>
-      </c>
-      <c r="P13" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>217</v>
-      </c>
-      <c r="R13" t="s">
-        <v>208</v>
-      </c>
-      <c r="U13" t="s">
-        <v>119</v>
-      </c>
-      <c r="V13" t="s">
-        <v>230</v>
-      </c>
-      <c r="W13" t="s">
-        <v>220</v>
-      </c>
-      <c r="X13" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B14" t="s">
-        <v>133</v>
-      </c>
-      <c r="C14">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D14">
-        <v>82.5</v>
-      </c>
-      <c r="E14">
-        <v>0.99550000000000005</v>
-      </c>
-      <c r="H14" t="s">
-        <v>175</v>
-      </c>
-      <c r="I14" t="s">
-        <v>164</v>
-      </c>
-      <c r="J14">
-        <v>4.3185124826726443E-2</v>
-      </c>
-      <c r="K14" t="s">
-        <v>165</v>
-      </c>
-      <c r="L14" t="s">
-        <v>164</v>
-      </c>
-      <c r="P14" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>207</v>
-      </c>
-      <c r="R14" t="s">
-        <v>208</v>
-      </c>
-      <c r="U14" t="s">
-        <v>119</v>
-      </c>
-      <c r="V14" t="s">
-        <v>231</v>
-      </c>
-      <c r="W14" t="s">
-        <v>220</v>
-      </c>
-      <c r="X14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
-        <v>134</v>
-      </c>
-      <c r="C15">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D15">
-        <v>31.900000000000002</v>
-      </c>
-      <c r="E15">
-        <v>0.99826000000000004</v>
-      </c>
-      <c r="H15" t="s">
-        <v>176</v>
-      </c>
-      <c r="I15" t="s">
-        <v>164</v>
-      </c>
-      <c r="J15">
-        <v>5.1713650970698723E-2</v>
-      </c>
-      <c r="K15" t="s">
-        <v>165</v>
-      </c>
-      <c r="L15" t="s">
-        <v>164</v>
-      </c>
-      <c r="P15" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>209</v>
-      </c>
-      <c r="R15" t="s">
-        <v>208</v>
-      </c>
-      <c r="U15" t="s">
-        <v>119</v>
-      </c>
-      <c r="V15" t="s">
-        <v>232</v>
-      </c>
-      <c r="W15" t="s">
-        <v>220</v>
-      </c>
-      <c r="X15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
-        <v>135</v>
-      </c>
-      <c r="C16">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D16">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="E16">
-        <v>0.99951999999999996</v>
-      </c>
-      <c r="H16" t="s">
-        <v>177</v>
-      </c>
-      <c r="I16" t="s">
-        <v>164</v>
-      </c>
-      <c r="J16">
-        <v>1.2144714448026258E-2</v>
-      </c>
-      <c r="K16" t="s">
-        <v>165</v>
-      </c>
-      <c r="L16" t="s">
-        <v>164</v>
-      </c>
-      <c r="P16" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>210</v>
-      </c>
-      <c r="R16" t="s">
-        <v>208</v>
-      </c>
-      <c r="U16" t="s">
-        <v>119</v>
-      </c>
-      <c r="V16" t="s">
-        <v>233</v>
-      </c>
-      <c r="W16" t="s">
-        <v>220</v>
-      </c>
-      <c r="X16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
-        <v>136</v>
-      </c>
-      <c r="C17">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D17">
-        <v>41.800000000000004</v>
-      </c>
-      <c r="E17">
-        <v>0.99772000000000005</v>
-      </c>
-      <c r="H17" t="s">
-        <v>178</v>
-      </c>
-      <c r="I17" t="s">
-        <v>164</v>
-      </c>
-      <c r="J17">
-        <v>7.392672774910522E-2</v>
-      </c>
-      <c r="K17" t="s">
-        <v>165</v>
-      </c>
-      <c r="L17" t="s">
-        <v>164</v>
-      </c>
-      <c r="P17" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>211</v>
-      </c>
-      <c r="R17" t="s">
-        <v>208</v>
-      </c>
-      <c r="U17" t="s">
-        <v>119</v>
-      </c>
-      <c r="V17" t="s">
-        <v>234</v>
-      </c>
-      <c r="W17" t="s">
-        <v>214</v>
-      </c>
-      <c r="X17" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C18">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D18">
-        <v>134.20000000000002</v>
-      </c>
-      <c r="E18">
-        <v>0.99268000000000001</v>
-      </c>
-      <c r="H18" t="s">
-        <v>179</v>
-      </c>
-      <c r="I18" t="s">
-        <v>164</v>
-      </c>
-      <c r="J18">
-        <v>3.633930313413767E-2</v>
-      </c>
-      <c r="K18" t="s">
-        <v>165</v>
-      </c>
-      <c r="L18" t="s">
-        <v>164</v>
-      </c>
-      <c r="P18" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>212</v>
-      </c>
-      <c r="R18" t="s">
-        <v>208</v>
-      </c>
-      <c r="U18" t="s">
-        <v>119</v>
-      </c>
-      <c r="V18" t="s">
-        <v>235</v>
-      </c>
-      <c r="W18" t="s">
-        <v>214</v>
-      </c>
-      <c r="X18" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
-        <v>138</v>
-      </c>
-      <c r="C19">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D19">
-        <v>3.3000000000000003</v>
-      </c>
-      <c r="E19">
-        <v>0.99982000000000004</v>
-      </c>
-      <c r="H19" t="s">
-        <v>180</v>
-      </c>
-      <c r="I19" t="s">
-        <v>164</v>
-      </c>
-      <c r="J19">
-        <v>3.5324533152767991E-2</v>
-      </c>
-      <c r="K19" t="s">
-        <v>165</v>
-      </c>
-      <c r="L19" t="s">
-        <v>164</v>
-      </c>
-      <c r="P19" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>213</v>
-      </c>
-      <c r="R19" t="s">
-        <v>208</v>
-      </c>
-      <c r="U19" t="s">
-        <v>119</v>
-      </c>
-      <c r="V19" t="s">
-        <v>236</v>
-      </c>
-      <c r="W19" t="s">
-        <v>214</v>
-      </c>
-      <c r="X19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C20">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D20">
-        <v>28.6</v>
-      </c>
-      <c r="E20">
-        <v>0.99843999999999999</v>
-      </c>
-      <c r="H20" t="s">
-        <v>181</v>
-      </c>
-      <c r="I20" t="s">
-        <v>164</v>
-      </c>
-      <c r="J20">
-        <v>3.5089155153095367E-2</v>
-      </c>
-      <c r="K20" t="s">
-        <v>165</v>
-      </c>
-      <c r="L20" t="s">
-        <v>164</v>
-      </c>
-      <c r="P20" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>214</v>
-      </c>
-      <c r="R20" t="s">
-        <v>208</v>
-      </c>
-      <c r="U20" t="s">
-        <v>119</v>
-      </c>
-      <c r="V20" t="s">
-        <v>237</v>
-      </c>
-      <c r="W20" t="s">
-        <v>238</v>
-      </c>
-      <c r="X20" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D21">
-        <v>50.6</v>
-      </c>
-      <c r="E21">
-        <v>0.99724000000000002</v>
-      </c>
-      <c r="H21" t="s">
-        <v>182</v>
-      </c>
-      <c r="I21" t="s">
-        <v>164</v>
-      </c>
-      <c r="J21">
-        <v>0.57933284097649596</v>
-      </c>
-      <c r="K21" t="s">
-        <v>165</v>
-      </c>
-      <c r="L21" t="s">
-        <v>164</v>
-      </c>
-      <c r="P21" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>215</v>
-      </c>
-      <c r="R21" t="s">
-        <v>208</v>
-      </c>
-      <c r="U21" t="s">
-        <v>119</v>
-      </c>
-      <c r="V21" t="s">
-        <v>239</v>
-      </c>
-      <c r="W21" t="s">
-        <v>238</v>
-      </c>
-      <c r="X21" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
-        <v>141</v>
-      </c>
-      <c r="C22">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D22">
-        <v>19.8</v>
-      </c>
-      <c r="E22">
-        <v>0.99892000000000003</v>
-      </c>
-      <c r="H22" t="s">
-        <v>183</v>
-      </c>
-      <c r="I22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J22">
-        <v>4.1164906764964301E-2</v>
-      </c>
-      <c r="K22" t="s">
-        <v>165</v>
-      </c>
-      <c r="L22" t="s">
-        <v>164</v>
-      </c>
-      <c r="P22" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>216</v>
-      </c>
-      <c r="R22" t="s">
-        <v>208</v>
-      </c>
-      <c r="U22" t="s">
-        <v>119</v>
-      </c>
-      <c r="V22" t="s">
-        <v>240</v>
-      </c>
-      <c r="W22" t="s">
-        <v>238</v>
-      </c>
-      <c r="X22" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
-        <v>142</v>
-      </c>
-      <c r="C23">
-        <v>3.5749528668221644</v>
-      </c>
-      <c r="D23">
-        <v>457.6</v>
-      </c>
-      <c r="E23">
-        <v>0.97504000000000002</v>
-      </c>
-      <c r="H23" t="s">
-        <v>184</v>
-      </c>
-      <c r="I23" t="s">
-        <v>164</v>
-      </c>
-      <c r="J23">
-        <v>7.1779042823981773E-2</v>
-      </c>
-      <c r="K23" t="s">
-        <v>165</v>
-      </c>
-      <c r="L23" t="s">
-        <v>164</v>
-      </c>
-      <c r="P23" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>217</v>
-      </c>
-      <c r="R23" t="s">
-        <v>208</v>
-      </c>
-      <c r="U23" t="s">
-        <v>119</v>
-      </c>
-      <c r="V23" t="s">
-        <v>241</v>
-      </c>
-      <c r="W23" t="s">
-        <v>209</v>
-      </c>
-      <c r="X23" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24">
-        <v>3.5749528668221644</v>
-      </c>
-      <c r="D24">
-        <v>104.50000000000001</v>
-      </c>
-      <c r="E24">
-        <v>0.99429999999999996</v>
-      </c>
-      <c r="H24" t="s">
-        <v>185</v>
-      </c>
-      <c r="I24" t="s">
-        <v>164</v>
-      </c>
-      <c r="J24">
-        <v>4.3185124826726443E-2</v>
-      </c>
-      <c r="K24" t="s">
-        <v>165</v>
-      </c>
-      <c r="L24" t="s">
-        <v>164</v>
-      </c>
-      <c r="P24" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R24" t="s">
-        <v>208</v>
-      </c>
-      <c r="U24" t="s">
-        <v>119</v>
-      </c>
-      <c r="V24" t="s">
-        <v>242</v>
-      </c>
-      <c r="W24" t="s">
-        <v>209</v>
-      </c>
-      <c r="X24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
-        <v>144</v>
-      </c>
-      <c r="C25">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D25">
-        <v>48.400000000000006</v>
-      </c>
-      <c r="E25">
-        <v>0.99736000000000002</v>
-      </c>
-      <c r="H25" t="s">
-        <v>186</v>
-      </c>
-      <c r="I25" t="s">
-        <v>164</v>
-      </c>
-      <c r="J25">
-        <v>5.1713650970698723E-2</v>
-      </c>
-      <c r="K25" t="s">
-        <v>165</v>
-      </c>
-      <c r="L25" t="s">
-        <v>164</v>
-      </c>
-      <c r="P25" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>209</v>
-      </c>
-      <c r="R25" t="s">
-        <v>208</v>
-      </c>
-      <c r="U25" t="s">
-        <v>119</v>
-      </c>
-      <c r="V25" t="s">
-        <v>243</v>
-      </c>
-      <c r="W25" t="s">
-        <v>209</v>
-      </c>
-      <c r="X25" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B26" t="s">
-        <v>145</v>
-      </c>
-      <c r="C26">
-        <v>3.5749528668221644</v>
-      </c>
-      <c r="D26">
-        <v>18.700000000000003</v>
-      </c>
-      <c r="E26">
-        <v>0.99897999999999998</v>
-      </c>
-      <c r="H26" t="s">
-        <v>187</v>
-      </c>
-      <c r="I26" t="s">
-        <v>164</v>
-      </c>
-      <c r="J26">
-        <v>1.2144714448026258E-2</v>
-      </c>
-      <c r="K26" t="s">
-        <v>165</v>
-      </c>
-      <c r="L26" t="s">
-        <v>164</v>
-      </c>
-      <c r="P26" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>210</v>
-      </c>
-      <c r="R26" t="s">
-        <v>208</v>
-      </c>
-      <c r="U26" t="s">
-        <v>119</v>
-      </c>
-      <c r="V26" t="s">
-        <v>244</v>
-      </c>
-      <c r="W26" t="s">
-        <v>245</v>
-      </c>
-      <c r="X26" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B27" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27">
-        <v>8.937382167055409</v>
-      </c>
-      <c r="D27">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E27">
-        <v>0.99987999999999999</v>
-      </c>
-      <c r="H27" t="s">
-        <v>188</v>
-      </c>
-      <c r="I27" t="s">
-        <v>164</v>
-      </c>
-      <c r="J27">
-        <v>7.392672774910522E-2</v>
-      </c>
-      <c r="K27" t="s">
-        <v>165</v>
-      </c>
-      <c r="L27" t="s">
-        <v>164</v>
-      </c>
-      <c r="P27" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>211</v>
-      </c>
-      <c r="R27" t="s">
-        <v>208</v>
-      </c>
-      <c r="U27" t="s">
-        <v>119</v>
-      </c>
-      <c r="V27" t="s">
-        <v>246</v>
-      </c>
-      <c r="W27" t="s">
-        <v>245</v>
-      </c>
-      <c r="X27" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
-        <v>147</v>
-      </c>
-      <c r="C28">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D28">
-        <v>72.600000000000009</v>
-      </c>
-      <c r="E28">
-        <v>0.99604000000000004</v>
-      </c>
-      <c r="H28" t="s">
-        <v>189</v>
-      </c>
-      <c r="I28" t="s">
-        <v>164</v>
-      </c>
-      <c r="J28">
-        <v>3.633930313413767E-2</v>
-      </c>
-      <c r="K28" t="s">
-        <v>165</v>
-      </c>
-      <c r="L28" t="s">
-        <v>164</v>
-      </c>
-      <c r="P28" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>212</v>
-      </c>
-      <c r="R28" t="s">
-        <v>208</v>
-      </c>
-      <c r="U28" t="s">
-        <v>119</v>
-      </c>
-      <c r="V28" t="s">
-        <v>247</v>
-      </c>
-      <c r="W28" t="s">
-        <v>245</v>
-      </c>
-      <c r="X28" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
-        <v>148</v>
-      </c>
-      <c r="C29">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D29">
-        <v>113.30000000000001</v>
-      </c>
-      <c r="E29">
-        <v>0.99382000000000004</v>
-      </c>
-      <c r="H29" t="s">
-        <v>190</v>
-      </c>
-      <c r="I29" t="s">
-        <v>164</v>
-      </c>
-      <c r="J29">
-        <v>3.5324533152767991E-2</v>
-      </c>
-      <c r="K29" t="s">
-        <v>165</v>
-      </c>
-      <c r="L29" t="s">
-        <v>164</v>
-      </c>
-      <c r="P29" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>213</v>
-      </c>
-      <c r="R29" t="s">
-        <v>208</v>
-      </c>
-      <c r="U29" t="s">
-        <v>119</v>
-      </c>
-      <c r="V29" t="s">
-        <v>248</v>
-      </c>
-      <c r="W29" t="s">
-        <v>211</v>
-      </c>
-      <c r="X29" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
-        <v>149</v>
-      </c>
-      <c r="C30">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D30">
-        <v>6.6000000000000005</v>
-      </c>
-      <c r="E30">
-        <v>0.99963999999999997</v>
-      </c>
-      <c r="H30" t="s">
-        <v>191</v>
-      </c>
-      <c r="I30" t="s">
-        <v>164</v>
-      </c>
-      <c r="J30">
-        <v>3.5089155153095367E-2</v>
-      </c>
-      <c r="K30" t="s">
-        <v>165</v>
-      </c>
-      <c r="L30" t="s">
-        <v>164</v>
-      </c>
-      <c r="P30" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>214</v>
-      </c>
-      <c r="R30" t="s">
-        <v>208</v>
-      </c>
-      <c r="U30" t="s">
-        <v>119</v>
-      </c>
-      <c r="V30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W30" t="s">
-        <v>211</v>
-      </c>
-      <c r="X30" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
-        <v>150</v>
-      </c>
-      <c r="C31">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D31">
-        <v>12.100000000000001</v>
-      </c>
-      <c r="E31">
-        <v>0.99934000000000001</v>
-      </c>
-      <c r="H31" t="s">
-        <v>192</v>
-      </c>
-      <c r="I31" t="s">
-        <v>164</v>
-      </c>
-      <c r="J31">
-        <v>0.57933284097649596</v>
-      </c>
-      <c r="K31" t="s">
-        <v>165</v>
-      </c>
-      <c r="L31" t="s">
-        <v>164</v>
-      </c>
-      <c r="P31" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>215</v>
-      </c>
-      <c r="R31" t="s">
-        <v>208</v>
-      </c>
-      <c r="U31" t="s">
-        <v>119</v>
-      </c>
-      <c r="V31" t="s">
-        <v>250</v>
-      </c>
-      <c r="W31" t="s">
-        <v>211</v>
-      </c>
-      <c r="X31" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
-        <v>151</v>
-      </c>
-      <c r="C32">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D32">
-        <v>447.70000000000005</v>
-      </c>
-      <c r="E32">
-        <v>0.97558</v>
-      </c>
-      <c r="H32" t="s">
-        <v>193</v>
-      </c>
-      <c r="I32" t="s">
-        <v>164</v>
-      </c>
-      <c r="J32">
-        <v>4.1164906764964301E-2</v>
-      </c>
-      <c r="K32" t="s">
-        <v>165</v>
-      </c>
-      <c r="L32" t="s">
-        <v>164</v>
-      </c>
-      <c r="P32" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>216</v>
-      </c>
-      <c r="R32" t="s">
-        <v>208</v>
-      </c>
-      <c r="U32" t="s">
-        <v>119</v>
-      </c>
-      <c r="V32" t="s">
-        <v>251</v>
-      </c>
-      <c r="W32" t="s">
-        <v>252</v>
-      </c>
-      <c r="X32" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B33" t="s">
-        <v>152</v>
-      </c>
-      <c r="C33">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D33">
-        <v>177.10000000000002</v>
-      </c>
-      <c r="E33">
-        <v>0.99034</v>
-      </c>
-      <c r="H33" t="s">
-        <v>194</v>
-      </c>
-      <c r="I33" t="s">
-        <v>164</v>
-      </c>
-      <c r="J33">
-        <v>7.1779042823981773E-2</v>
-      </c>
-      <c r="K33" t="s">
-        <v>165</v>
-      </c>
-      <c r="L33" t="s">
-        <v>164</v>
-      </c>
-      <c r="P33" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>217</v>
-      </c>
-      <c r="R33" t="s">
-        <v>208</v>
-      </c>
-      <c r="U33" t="s">
-        <v>119</v>
-      </c>
-      <c r="V33" t="s">
-        <v>253</v>
-      </c>
-      <c r="W33" t="s">
-        <v>252</v>
-      </c>
-      <c r="X33" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B34" t="s">
-        <v>153</v>
-      </c>
-      <c r="C34">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D34">
-        <v>79.2</v>
-      </c>
-      <c r="E34">
-        <v>0.99568000000000001</v>
-      </c>
-      <c r="H34" t="s">
-        <v>195</v>
-      </c>
-      <c r="I34" t="s">
-        <v>164</v>
-      </c>
-      <c r="J34">
-        <v>4.3185124826726443E-2</v>
-      </c>
-      <c r="K34" t="s">
-        <v>165</v>
-      </c>
-      <c r="L34" t="s">
-        <v>164</v>
-      </c>
-      <c r="P34" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>207</v>
-      </c>
-      <c r="R34" t="s">
-        <v>208</v>
-      </c>
-      <c r="U34" t="s">
-        <v>119</v>
-      </c>
-      <c r="V34" t="s">
-        <v>254</v>
-      </c>
-      <c r="W34" t="s">
-        <v>252</v>
-      </c>
-      <c r="X34" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B35" t="s">
-        <v>154</v>
-      </c>
-      <c r="C35">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D35">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="E35">
-        <v>0.99975999999999998</v>
-      </c>
-      <c r="H35" t="s">
-        <v>196</v>
-      </c>
-      <c r="I35" t="s">
-        <v>164</v>
-      </c>
-      <c r="J35">
-        <v>5.1713650970698723E-2</v>
-      </c>
-      <c r="K35" t="s">
-        <v>165</v>
-      </c>
-      <c r="L35" t="s">
-        <v>164</v>
-      </c>
-      <c r="P35" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>209</v>
-      </c>
-      <c r="R35" t="s">
-        <v>208</v>
-      </c>
-      <c r="U35" t="s">
-        <v>119</v>
-      </c>
-      <c r="V35" t="s">
-        <v>255</v>
-      </c>
-      <c r="W35" t="s">
-        <v>256</v>
-      </c>
-      <c r="X35" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B36" t="s">
-        <v>155</v>
-      </c>
-      <c r="C36">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D36">
-        <v>14.3</v>
-      </c>
-      <c r="E36">
-        <v>0.99922</v>
-      </c>
-      <c r="H36" t="s">
-        <v>197</v>
-      </c>
-      <c r="I36" t="s">
-        <v>164</v>
-      </c>
-      <c r="J36">
-        <v>1.2144714448026258E-2</v>
-      </c>
-      <c r="K36" t="s">
-        <v>165</v>
-      </c>
-      <c r="L36" t="s">
-        <v>164</v>
-      </c>
-      <c r="P36" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>210</v>
-      </c>
-      <c r="R36" t="s">
-        <v>208</v>
-      </c>
-      <c r="U36" t="s">
-        <v>119</v>
-      </c>
-      <c r="V36" t="s">
-        <v>257</v>
-      </c>
-      <c r="W36" t="s">
-        <v>256</v>
-      </c>
-      <c r="X36" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B37" t="s">
-        <v>156</v>
-      </c>
-      <c r="C37">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D37">
-        <v>130.9</v>
-      </c>
-      <c r="E37">
-        <v>0.99285999999999996</v>
-      </c>
-      <c r="H37" t="s">
-        <v>198</v>
-      </c>
-      <c r="I37" t="s">
-        <v>164</v>
-      </c>
-      <c r="J37">
-        <v>7.392672774910522E-2</v>
-      </c>
-      <c r="K37" t="s">
-        <v>165</v>
-      </c>
-      <c r="L37" t="s">
-        <v>164</v>
-      </c>
-      <c r="P37" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>211</v>
-      </c>
-      <c r="R37" t="s">
-        <v>208</v>
-      </c>
-      <c r="U37" t="s">
-        <v>119</v>
-      </c>
-      <c r="V37" t="s">
-        <v>258</v>
-      </c>
-      <c r="W37" t="s">
-        <v>256</v>
-      </c>
-      <c r="X37" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B38" t="s">
-        <v>157</v>
-      </c>
-      <c r="C38">
-        <v>0.98311203837609484</v>
-      </c>
-      <c r="D38">
-        <v>25.3</v>
-      </c>
-      <c r="E38">
-        <v>0.99861999999999995</v>
-      </c>
-      <c r="H38" t="s">
-        <v>199</v>
-      </c>
-      <c r="I38" t="s">
-        <v>164</v>
-      </c>
-      <c r="J38">
-        <v>3.633930313413767E-2</v>
-      </c>
-      <c r="K38" t="s">
-        <v>165</v>
-      </c>
-      <c r="L38" t="s">
-        <v>164</v>
-      </c>
-      <c r="P38" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>212</v>
-      </c>
-      <c r="R38" t="s">
-        <v>208</v>
-      </c>
-      <c r="U38" t="s">
-        <v>119</v>
-      </c>
-      <c r="V38" t="s">
-        <v>259</v>
-      </c>
-      <c r="W38" t="s">
-        <v>220</v>
-      </c>
-      <c r="X38" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B39" t="s">
-        <v>158</v>
-      </c>
-      <c r="C39">
-        <v>0.49155601918804742</v>
-      </c>
-      <c r="D39">
-        <v>110.00000000000001</v>
-      </c>
-      <c r="E39">
-        <v>0.99399999999999999</v>
-      </c>
-      <c r="H39" t="s">
-        <v>200</v>
-      </c>
-      <c r="I39" t="s">
-        <v>164</v>
-      </c>
-      <c r="J39">
-        <v>3.5324533152767991E-2</v>
-      </c>
-      <c r="K39" t="s">
-        <v>165</v>
-      </c>
-      <c r="L39" t="s">
-        <v>164</v>
-      </c>
-      <c r="P39" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>213</v>
-      </c>
-      <c r="R39" t="s">
-        <v>208</v>
-      </c>
-      <c r="U39" t="s">
-        <v>119</v>
-      </c>
-      <c r="V39" t="s">
-        <v>260</v>
-      </c>
-      <c r="W39" t="s">
-        <v>220</v>
-      </c>
-      <c r="X39" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="H40" t="s">
-        <v>201</v>
-      </c>
-      <c r="I40" t="s">
-        <v>164</v>
-      </c>
-      <c r="J40">
-        <v>3.5089155153095367E-2</v>
-      </c>
-      <c r="K40" t="s">
-        <v>165</v>
-      </c>
-      <c r="L40" t="s">
-        <v>164</v>
-      </c>
-      <c r="P40" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>214</v>
-      </c>
-      <c r="R40" t="s">
-        <v>208</v>
-      </c>
-      <c r="U40" t="s">
-        <v>119</v>
-      </c>
-      <c r="V40" t="s">
-        <v>261</v>
-      </c>
-      <c r="W40" t="s">
-        <v>216</v>
-      </c>
-      <c r="X40" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="H41" t="s">
-        <v>202</v>
-      </c>
-      <c r="I41" t="s">
-        <v>164</v>
-      </c>
-      <c r="J41">
-        <v>0.57933284097649596</v>
-      </c>
-      <c r="K41" t="s">
-        <v>165</v>
-      </c>
-      <c r="L41" t="s">
-        <v>164</v>
-      </c>
-      <c r="P41" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>215</v>
-      </c>
-      <c r="R41" t="s">
-        <v>208</v>
-      </c>
-      <c r="U41" t="s">
-        <v>119</v>
-      </c>
-      <c r="V41" t="s">
-        <v>262</v>
-      </c>
-      <c r="W41" t="s">
-        <v>216</v>
-      </c>
-      <c r="X41" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="H42" t="s">
-        <v>203</v>
-      </c>
-      <c r="I42" t="s">
-        <v>164</v>
-      </c>
-      <c r="J42">
-        <v>4.1164906764964301E-2</v>
-      </c>
-      <c r="K42" t="s">
-        <v>165</v>
-      </c>
-      <c r="L42" t="s">
-        <v>164</v>
-      </c>
-      <c r="P42" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>216</v>
-      </c>
-      <c r="R42" t="s">
-        <v>208</v>
-      </c>
-      <c r="U42" t="s">
-        <v>119</v>
-      </c>
-      <c r="V42" t="s">
-        <v>263</v>
-      </c>
-      <c r="W42" t="s">
-        <v>215</v>
-      </c>
-      <c r="X42" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="H43" t="s">
-        <v>204</v>
-      </c>
-      <c r="I43" t="s">
-        <v>164</v>
-      </c>
-      <c r="J43">
-        <v>7.1779042823981773E-2</v>
-      </c>
-      <c r="K43" t="s">
-        <v>165</v>
-      </c>
-      <c r="L43" t="s">
-        <v>164</v>
-      </c>
-      <c r="P43" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>217</v>
-      </c>
-      <c r="R43" t="s">
-        <v>208</v>
-      </c>
-      <c r="U43" t="s">
-        <v>119</v>
-      </c>
-      <c r="V43" t="s">
-        <v>264</v>
-      </c>
-      <c r="W43" t="s">
-        <v>215</v>
-      </c>
-      <c r="X43" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="U44" t="s">
-        <v>119</v>
-      </c>
-      <c r="V44" t="s">
-        <v>265</v>
-      </c>
-      <c r="W44" t="s">
-        <v>266</v>
-      </c>
-      <c r="X44" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="U45" t="s">
-        <v>119</v>
-      </c>
-      <c r="V45" t="s">
-        <v>267</v>
-      </c>
-      <c r="W45" t="s">
-        <v>266</v>
-      </c>
-      <c r="X45" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="U46" t="s">
-        <v>119</v>
-      </c>
-      <c r="V46" t="s">
-        <v>268</v>
-      </c>
-      <c r="W46" t="s">
-        <v>211</v>
-      </c>
-      <c r="X46" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="U47" t="s">
-        <v>119</v>
-      </c>
-      <c r="V47" t="s">
-        <v>269</v>
-      </c>
-      <c r="W47" t="s">
-        <v>211</v>
-      </c>
-      <c r="X47" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="U48" t="s">
-        <v>119</v>
-      </c>
-      <c r="V48" t="s">
-        <v>270</v>
-      </c>
-      <c r="W48" t="s">
-        <v>210</v>
-      </c>
-      <c r="X48" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="49" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U49" t="s">
-        <v>119</v>
-      </c>
-      <c r="V49" t="s">
-        <v>271</v>
-      </c>
-      <c r="W49" t="s">
-        <v>210</v>
-      </c>
-      <c r="X49" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="50" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U50" t="s">
-        <v>119</v>
-      </c>
-      <c r="V50" t="s">
-        <v>272</v>
-      </c>
-      <c r="W50" t="s">
-        <v>212</v>
-      </c>
-      <c r="X50" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="51" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U51" t="s">
-        <v>119</v>
-      </c>
-      <c r="V51" t="s">
-        <v>273</v>
-      </c>
-      <c r="W51" t="s">
-        <v>212</v>
-      </c>
-      <c r="X51" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="52" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U52" t="s">
-        <v>119</v>
-      </c>
-      <c r="V52" t="s">
-        <v>274</v>
-      </c>
-      <c r="W52" t="s">
-        <v>275</v>
-      </c>
-      <c r="X52" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="53" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U53" t="s">
-        <v>119</v>
-      </c>
-      <c r="V53" t="s">
-        <v>276</v>
-      </c>
-      <c r="W53" t="s">
-        <v>275</v>
-      </c>
-      <c r="X53" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="54" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U54" t="s">
-        <v>119</v>
-      </c>
-      <c r="V54" t="s">
-        <v>277</v>
-      </c>
-      <c r="W54" t="s">
-        <v>217</v>
-      </c>
-      <c r="X54" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="55" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U55" t="s">
-        <v>119</v>
-      </c>
-      <c r="V55" t="s">
-        <v>278</v>
-      </c>
-      <c r="W55" t="s">
-        <v>217</v>
-      </c>
-      <c r="X55" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="56" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U56" t="s">
-        <v>119</v>
-      </c>
-      <c r="V56" t="s">
-        <v>279</v>
-      </c>
-      <c r="W56" t="s">
-        <v>214</v>
-      </c>
-      <c r="X56" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="57" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U57" t="s">
-        <v>119</v>
-      </c>
-      <c r="V57" t="s">
-        <v>280</v>
-      </c>
-      <c r="W57" t="s">
-        <v>214</v>
-      </c>
-      <c r="X57" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U58" t="s">
-        <v>119</v>
-      </c>
-      <c r="V58" t="s">
-        <v>281</v>
-      </c>
-      <c r="W58" t="s">
-        <v>256</v>
-      </c>
-      <c r="X58" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="59" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U59" t="s">
-        <v>119</v>
-      </c>
-      <c r="V59" t="s">
-        <v>282</v>
-      </c>
-      <c r="W59" t="s">
-        <v>256</v>
-      </c>
-      <c r="X59" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="60" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U60" t="s">
-        <v>119</v>
-      </c>
-      <c r="V60" t="s">
-        <v>283</v>
-      </c>
-      <c r="W60" t="s">
-        <v>284</v>
-      </c>
-      <c r="X60" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="61" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U61" t="s">
-        <v>119</v>
-      </c>
-      <c r="V61" t="s">
-        <v>285</v>
-      </c>
-      <c r="W61" t="s">
-        <v>284</v>
-      </c>
-      <c r="X61" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="62" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U62" t="s">
-        <v>119</v>
-      </c>
-      <c r="V62" t="s">
-        <v>286</v>
-      </c>
-      <c r="W62" t="s">
-        <v>287</v>
-      </c>
-      <c r="X62" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="63" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U63" t="s">
-        <v>119</v>
-      </c>
-      <c r="V63" t="s">
-        <v>288</v>
-      </c>
-      <c r="W63" t="s">
-        <v>287</v>
-      </c>
-      <c r="X63" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="64" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U64" t="s">
-        <v>119</v>
-      </c>
-      <c r="V64" t="s">
-        <v>289</v>
-      </c>
-      <c r="W64" t="s">
-        <v>290</v>
-      </c>
-      <c r="X64" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="65" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U65" t="s">
-        <v>119</v>
-      </c>
-      <c r="V65" t="s">
-        <v>291</v>
-      </c>
-      <c r="W65" t="s">
-        <v>290</v>
-      </c>
-      <c r="X65" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="66" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U66" t="s">
-        <v>119</v>
-      </c>
-      <c r="V66" t="s">
-        <v>292</v>
-      </c>
-      <c r="W66" t="s">
-        <v>293</v>
-      </c>
-      <c r="X66" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="67" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U67" t="s">
-        <v>119</v>
-      </c>
-      <c r="V67" t="s">
-        <v>294</v>
-      </c>
-      <c r="W67" t="s">
-        <v>293</v>
-      </c>
-      <c r="X67" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="68" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U68" t="s">
-        <v>119</v>
-      </c>
-      <c r="V68" t="s">
-        <v>295</v>
-      </c>
-      <c r="W68" t="s">
-        <v>296</v>
-      </c>
-      <c r="X68" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="69" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U69" t="s">
-        <v>119</v>
-      </c>
-      <c r="V69" t="s">
-        <v>297</v>
-      </c>
-      <c r="W69" t="s">
-        <v>296</v>
-      </c>
-      <c r="X69" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="70" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U70" t="s">
-        <v>119</v>
-      </c>
-      <c r="V70" t="s">
-        <v>298</v>
-      </c>
-      <c r="W70" t="s">
-        <v>299</v>
-      </c>
-      <c r="X70" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="71" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U71" t="s">
-        <v>119</v>
-      </c>
-      <c r="V71" t="s">
-        <v>300</v>
-      </c>
-      <c r="W71" t="s">
-        <v>299</v>
-      </c>
-      <c r="X71" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="72" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U72" t="s">
-        <v>119</v>
-      </c>
-      <c r="V72" t="s">
-        <v>301</v>
-      </c>
-      <c r="W72" t="s">
-        <v>238</v>
-      </c>
-      <c r="X72" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="73" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U73" t="s">
-        <v>119</v>
-      </c>
-      <c r="V73" t="s">
-        <v>302</v>
-      </c>
-      <c r="W73" t="s">
-        <v>238</v>
-      </c>
-      <c r="X73" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="74" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U74" t="s">
-        <v>119</v>
-      </c>
-      <c r="V74" t="s">
-        <v>303</v>
-      </c>
-      <c r="W74" t="s">
-        <v>209</v>
-      </c>
-      <c r="X74" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="75" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U75" t="s">
-        <v>119</v>
-      </c>
-      <c r="V75" t="s">
-        <v>304</v>
-      </c>
-      <c r="W75" t="s">
-        <v>209</v>
-      </c>
-      <c r="X75" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="76" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U76" t="s">
-        <v>119</v>
-      </c>
-      <c r="V76" t="s">
-        <v>305</v>
-      </c>
-      <c r="W76" t="s">
-        <v>245</v>
-      </c>
-      <c r="X76" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="77" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U77" t="s">
-        <v>119</v>
-      </c>
-      <c r="V77" t="s">
-        <v>306</v>
-      </c>
-      <c r="W77" t="s">
-        <v>245</v>
-      </c>
-      <c r="X77" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="78" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U78" t="s">
-        <v>119</v>
-      </c>
-      <c r="V78" t="s">
-        <v>307</v>
-      </c>
-      <c r="W78" t="s">
-        <v>252</v>
-      </c>
-      <c r="X78" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="79" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U79" t="s">
-        <v>119</v>
-      </c>
-      <c r="V79" t="s">
-        <v>308</v>
-      </c>
-      <c r="W79" t="s">
-        <v>252</v>
-      </c>
-      <c r="X79" t="s">
-        <v>221</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB447BB-E8CA-4214-9E20-B3262CBB4470}">
-  <dimension ref="B9:L26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H10" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" t="s">
-        <v>100</v>
-      </c>
-      <c r="L10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B11">
-        <v>2030</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" t="s">
-        <v>105</v>
-      </c>
-      <c r="H11" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J11" t="s">
-        <v>107</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B12">
-        <v>2030</v>
-      </c>
-      <c r="C12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12">
-        <v>0.67</v>
-      </c>
-      <c r="F12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" t="s">
-        <v>105</v>
-      </c>
-      <c r="H12" t="s">
-        <v>106</v>
-      </c>
-      <c r="I12" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J12" t="s">
-        <v>107</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B13">
-        <v>2030</v>
-      </c>
-      <c r="C13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" t="s">
-        <v>106</v>
-      </c>
-      <c r="I13" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J13" t="s">
-        <v>107</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B14">
-        <v>2030</v>
-      </c>
-      <c r="C14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14">
-        <v>1.67</v>
-      </c>
-      <c r="F14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" t="s">
-        <v>105</v>
-      </c>
-      <c r="H14" t="s">
-        <v>106</v>
-      </c>
-      <c r="I14" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J14" t="s">
-        <v>107</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B15">
-        <v>2030</v>
-      </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15">
-        <v>2.67</v>
-      </c>
-      <c r="F15" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" t="s">
-        <v>105</v>
-      </c>
-      <c r="H15" t="s">
-        <v>106</v>
-      </c>
-      <c r="I15" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J15" t="s">
-        <v>107</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B16">
-        <v>2030</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16">
-        <v>3.67</v>
-      </c>
-      <c r="F16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" t="s">
-        <v>106</v>
-      </c>
-      <c r="I16" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J16" t="s">
-        <v>107</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B17">
-        <v>2030</v>
-      </c>
-      <c r="C17" t="s">
-        <v>115</v>
-      </c>
-      <c r="D17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17">
-        <v>28</v>
-      </c>
-      <c r="F17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" t="s">
-        <v>106</v>
-      </c>
-      <c r="I17" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J17" t="s">
-        <v>107</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B18">
-        <v>2030</v>
-      </c>
-      <c r="C18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18">
-        <v>8.07</v>
-      </c>
-      <c r="F18" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" t="s">
-        <v>105</v>
-      </c>
-      <c r="H18" t="s">
-        <v>106</v>
-      </c>
-      <c r="I18" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J18" t="s">
-        <v>107</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B19">
-        <v>2030</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19">
-        <v>6.6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>104</v>
-      </c>
-      <c r="G19" t="s">
-        <v>105</v>
-      </c>
-      <c r="H19" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J19" t="s">
-        <v>107</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B20">
-        <v>2030</v>
-      </c>
-      <c r="C20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" t="s">
-        <v>105</v>
-      </c>
-      <c r="H20" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J20" t="s">
-        <v>107</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B21">
-        <v>2030</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21">
-        <v>3.67</v>
-      </c>
-      <c r="F21" t="s">
-        <v>104</v>
-      </c>
-      <c r="G21" t="s">
-        <v>105</v>
-      </c>
-      <c r="H21" t="s">
-        <v>106</v>
-      </c>
-      <c r="I21" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J21" t="s">
-        <v>107</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B22">
-        <v>2030</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>116</v>
-      </c>
-      <c r="E22">
-        <v>11.11</v>
-      </c>
-      <c r="F22" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" t="s">
-        <v>105</v>
-      </c>
-      <c r="H22" t="s">
-        <v>106</v>
-      </c>
-      <c r="I22" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J22" t="s">
-        <v>107</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B23">
-        <v>2030</v>
-      </c>
-      <c r="C23" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23">
-        <v>24.44</v>
-      </c>
-      <c r="F23" t="s">
-        <v>104</v>
-      </c>
-      <c r="G23" t="s">
-        <v>105</v>
-      </c>
-      <c r="H23" t="s">
-        <v>106</v>
-      </c>
-      <c r="I23" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J23" t="s">
-        <v>107</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B24">
-        <v>2030</v>
-      </c>
-      <c r="C24" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" t="s">
-        <v>116</v>
-      </c>
-      <c r="E24">
-        <v>20</v>
-      </c>
-      <c r="F24" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" t="s">
-        <v>105</v>
-      </c>
-      <c r="H24" t="s">
-        <v>106</v>
-      </c>
-      <c r="I24" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J24" t="s">
-        <v>107</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B25">
-        <v>2030</v>
-      </c>
-      <c r="C25" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25">
-        <v>33.33</v>
-      </c>
-      <c r="F25" t="s">
-        <v>104</v>
-      </c>
-      <c r="G25" t="s">
-        <v>105</v>
-      </c>
-      <c r="H25" t="s">
-        <v>106</v>
-      </c>
-      <c r="I25" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J25" t="s">
-        <v>107</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B26">
-        <v>2030</v>
-      </c>
-      <c r="C26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26">
-        <v>11.11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>104</v>
-      </c>
-      <c r="G26" t="s">
-        <v>105</v>
-      </c>
-      <c r="H26" t="s">
-        <v>106</v>
-      </c>
-      <c r="I26" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J26" t="s">
-        <v>107</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5525,12 +5527,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -5559,7 +5561,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -9024,7 +9026,7 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B250">
         <v>2000</v>
@@ -9150,7 +9152,7 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B259">
         <v>2001</v>
@@ -9276,7 +9278,7 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B268">
         <v>2002</v>
@@ -9402,7 +9404,7 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B277">
         <v>2003</v>
@@ -9528,7 +9530,7 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B286">
         <v>2004</v>
@@ -9654,7 +9656,7 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B295">
         <v>2005</v>
@@ -9780,7 +9782,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B304">
         <v>2006</v>
@@ -9906,7 +9908,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B313">
         <v>2007</v>
@@ -10032,7 +10034,7 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B322">
         <v>2008</v>
@@ -10158,7 +10160,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B331">
         <v>2009</v>
@@ -10284,7 +10286,7 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B340">
         <v>2010</v>
@@ -10410,7 +10412,7 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B349">
         <v>2011</v>
@@ -10536,7 +10538,7 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B358">
         <v>2012</v>
@@ -10662,7 +10664,7 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B367">
         <v>2013</v>
@@ -10788,7 +10790,7 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B376">
         <v>2014</v>
@@ -10914,7 +10916,7 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B385">
         <v>2015</v>
@@ -11040,7 +11042,7 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B394">
         <v>2016</v>
@@ -11166,7 +11168,7 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B403">
         <v>2017</v>
@@ -11292,7 +11294,7 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B412">
         <v>2018</v>
@@ -11418,7 +11420,7 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B421">
         <v>2019</v>
@@ -11544,7 +11546,7 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B430">
         <v>2020</v>
@@ -11670,7 +11672,7 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B439">
         <v>2021</v>
@@ -11796,7 +11798,7 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B448">
         <v>2022</v>
@@ -11922,7 +11924,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B457">
         <v>2023</v>
@@ -12468,7 +12470,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B496">
         <v>2018</v>
@@ -12482,7 +12484,7 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B497">
         <v>2019</v>
@@ -12496,7 +12498,7 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B498">
         <v>2020</v>
@@ -12510,7 +12512,7 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B499">
         <v>2021</v>
@@ -12524,7 +12526,7 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B500">
         <v>2022</v>
@@ -12538,7 +12540,7 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B501">
         <v>2023</v>
@@ -12552,7 +12554,7 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B502">
         <v>2024</v>
@@ -12566,7 +12568,7 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B503">
         <v>2011</v>
@@ -12580,7 +12582,7 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B504">
         <v>2012</v>
@@ -12594,7 +12596,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B505">
         <v>2013</v>
@@ -12608,7 +12610,7 @@
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B506">
         <v>2014</v>
@@ -12622,7 +12624,7 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B507">
         <v>2015</v>
@@ -12636,7 +12638,7 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B508">
         <v>2016</v>
@@ -12650,7 +12652,7 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B509">
         <v>2017</v>
@@ -12664,7 +12666,7 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B510">
         <v>2004</v>
@@ -12678,7 +12680,7 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B511">
         <v>2005</v>
@@ -12692,7 +12694,7 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B512">
         <v>2006</v>
@@ -12706,7 +12708,7 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B513">
         <v>2007</v>
@@ -12720,7 +12722,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B514">
         <v>2008</v>
@@ -12734,7 +12736,7 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B515">
         <v>2009</v>
@@ -12748,7 +12750,7 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B516">
         <v>2010</v>
@@ -12762,7 +12764,7 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B517">
         <v>2000</v>
@@ -12776,7 +12778,7 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B518">
         <v>2001</v>
@@ -12790,7 +12792,7 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B519">
         <v>2002</v>
@@ -12804,7 +12806,7 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B520">
         <v>2003</v>
@@ -12818,7 +12820,7 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B521">
         <v>2002</v>
@@ -12832,7 +12834,7 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B522">
         <v>2003</v>
@@ -12846,7 +12848,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B523">
         <v>2004</v>
@@ -12860,7 +12862,7 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B524">
         <v>2005</v>
@@ -12874,7 +12876,7 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B525">
         <v>2006</v>
@@ -12888,7 +12890,7 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B526">
         <v>2007</v>
@@ -12902,7 +12904,7 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B527">
         <v>2008</v>
@@ -12916,7 +12918,7 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B528">
         <v>2009</v>
@@ -12930,7 +12932,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B529">
         <v>2010</v>
@@ -12944,7 +12946,7 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B530">
         <v>2011</v>
@@ -12958,7 +12960,7 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B531">
         <v>2012</v>
@@ -12972,7 +12974,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B532">
         <v>2013</v>
@@ -12986,7 +12988,7 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B533">
         <v>2014</v>
@@ -13000,7 +13002,7 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B534">
         <v>2015</v>
@@ -13014,7 +13016,7 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B535">
         <v>2016</v>
@@ -13028,7 +13030,7 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B536">
         <v>2017</v>
@@ -13042,7 +13044,7 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B537">
         <v>2018</v>
@@ -13056,7 +13058,7 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B538">
         <v>2019</v>
@@ -13070,7 +13072,7 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B539">
         <v>2020</v>
@@ -13084,7 +13086,7 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B540">
         <v>2021</v>
@@ -13098,7 +13100,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B541">
         <v>2022</v>
@@ -13112,7 +13114,7 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B542">
         <v>2000</v>
@@ -13126,7 +13128,7 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B543">
         <v>2001</v>
@@ -14204,7 +14206,7 @@
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A620" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B620">
         <v>2018</v>
@@ -14218,7 +14220,7 @@
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A621" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B621">
         <v>2019</v>
@@ -14232,7 +14234,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B622">
         <v>2020</v>
@@ -14246,7 +14248,7 @@
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A623" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B623">
         <v>2021</v>
@@ -14260,7 +14262,7 @@
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A624" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B624">
         <v>2022</v>
@@ -14274,7 +14276,7 @@
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A625" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B625">
         <v>2023</v>
@@ -14288,7 +14290,7 @@
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A626" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B626">
         <v>2024</v>
@@ -14302,7 +14304,7 @@
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A627" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B627">
         <v>2011</v>
@@ -14316,7 +14318,7 @@
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A628" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B628">
         <v>2012</v>
@@ -14330,7 +14332,7 @@
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A629" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B629">
         <v>2013</v>
@@ -14344,7 +14346,7 @@
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A630" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B630">
         <v>2014</v>
@@ -14358,7 +14360,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B631">
         <v>2015</v>
@@ -14372,7 +14374,7 @@
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A632" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B632">
         <v>2016</v>
@@ -14386,7 +14388,7 @@
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A633" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B633">
         <v>2017</v>
@@ -14400,7 +14402,7 @@
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A634" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B634">
         <v>2004</v>
@@ -14414,7 +14416,7 @@
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A635" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B635">
         <v>2005</v>
@@ -14428,7 +14430,7 @@
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A636" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B636">
         <v>2006</v>
@@ -14442,7 +14444,7 @@
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A637" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B637">
         <v>2007</v>
@@ -14456,7 +14458,7 @@
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A638" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B638">
         <v>2008</v>
@@ -14470,7 +14472,7 @@
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A639" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B639">
         <v>2009</v>
@@ -14484,7 +14486,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B640">
         <v>2010</v>
@@ -14498,7 +14500,7 @@
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A641" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B641">
         <v>2000</v>
@@ -14512,7 +14514,7 @@
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A642" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B642">
         <v>2001</v>
@@ -14526,7 +14528,7 @@
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A643" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B643">
         <v>2002</v>
@@ -14540,7 +14542,7 @@
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A644" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B644">
         <v>2003</v>
@@ -14554,7 +14556,7 @@
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A645" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B645">
         <v>2002</v>
@@ -14568,7 +14570,7 @@
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A646" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B646">
         <v>2003</v>
@@ -14582,7 +14584,7 @@
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A647" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B647">
         <v>2004</v>
@@ -14596,7 +14598,7 @@
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A648" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B648">
         <v>2005</v>
@@ -14610,7 +14612,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B649">
         <v>2006</v>
@@ -14624,7 +14626,7 @@
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A650" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B650">
         <v>2007</v>
@@ -14638,7 +14640,7 @@
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A651" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B651">
         <v>2008</v>
@@ -14652,7 +14654,7 @@
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A652" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B652">
         <v>2009</v>
@@ -14666,7 +14668,7 @@
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A653" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B653">
         <v>2010</v>
@@ -14680,7 +14682,7 @@
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A654" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B654">
         <v>2011</v>
@@ -14694,7 +14696,7 @@
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A655" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B655">
         <v>2012</v>
@@ -14708,7 +14710,7 @@
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A656" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B656">
         <v>2013</v>
@@ -14722,7 +14724,7 @@
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A657" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B657">
         <v>2014</v>
@@ -14736,7 +14738,7 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A658" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B658">
         <v>2015</v>
@@ -14750,7 +14752,7 @@
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A659" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B659">
         <v>2016</v>
@@ -14764,7 +14766,7 @@
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A660" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B660">
         <v>2017</v>
@@ -14778,7 +14780,7 @@
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A661" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B661">
         <v>2018</v>
@@ -14792,7 +14794,7 @@
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A662" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B662">
         <v>2019</v>
@@ -14806,7 +14808,7 @@
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A663" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B663">
         <v>2020</v>
@@ -14820,7 +14822,7 @@
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A664" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B664">
         <v>2021</v>
@@ -14834,7 +14836,7 @@
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A665" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B665">
         <v>2022</v>
@@ -14848,7 +14850,7 @@
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A666" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B666">
         <v>2000</v>
@@ -14862,7 +14864,7 @@
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A667" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B667">
         <v>2001</v>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BA0189F-24EA-4219-853B-C5CA98F04937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29D3F0E1-6FAC-4B1F-B360-A949D60C7B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1578,7 +1578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734D939D-8184-435E-B479-8BDCF3F17917}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5D64F71-C112-40C7-99BC-DEA08795C991}">
   <dimension ref="B2:AF79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4159,7 +4159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26CB159B-A929-4386-8CD3-4249F9D23578}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1071A8CA-F185-4E7E-A9F0-EE7B7EDEB5F0}">
   <dimension ref="B9:L26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
